--- a/skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx
+++ b/skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx
@@ -83,17 +83,41 @@
     <definedName function="false" hidden="false" name="cqB_8" vbProcedure="false">In!$E$100</definedName>
     <definedName function="false" hidden="false" name="cqB_9" vbProcedure="false">In!$E$101</definedName>
     <definedName function="false" hidden="false" name="cqC_10" vbProcedure="false">In!$E$114</definedName>
+    <definedName function="false" hidden="false" name="cqC_10_hi" vbProcedure="false">In!$F$114</definedName>
+    <definedName function="false" hidden="false" name="cqC_10_lo" vbProcedure="false">In!$D$114</definedName>
     <definedName function="false" hidden="false" name="cqC_11" vbProcedure="false">In!$E$115</definedName>
+    <definedName function="false" hidden="false" name="cqC_11_hi" vbProcedure="false">In!$F$115</definedName>
+    <definedName function="false" hidden="false" name="cqC_11_lo" vbProcedure="false">In!$D$115</definedName>
     <definedName function="false" hidden="false" name="cqC_12" vbProcedure="false">In!$E$116</definedName>
+    <definedName function="false" hidden="false" name="cqC_12_hi" vbProcedure="false">In!$F$116</definedName>
+    <definedName function="false" hidden="false" name="cqC_12_lo" vbProcedure="false">In!$D$116</definedName>
     <definedName function="false" hidden="false" name="cqC_13" vbProcedure="false">In!$E$117</definedName>
+    <definedName function="false" hidden="false" name="cqC_13_hi" vbProcedure="false">In!$F$117</definedName>
+    <definedName function="false" hidden="false" name="cqC_13_lo" vbProcedure="false">In!$D$117</definedName>
     <definedName function="false" hidden="false" name="cqC_14" vbProcedure="false">In!$E$118</definedName>
+    <definedName function="false" hidden="false" name="cqC_14_hi" vbProcedure="false">In!$F$118</definedName>
+    <definedName function="false" hidden="false" name="cqC_14_lo" vbProcedure="false">In!$D$118</definedName>
     <definedName function="false" hidden="false" name="cqC_15" vbProcedure="false">In!$E$119</definedName>
+    <definedName function="false" hidden="false" name="cqC_15_hi" vbProcedure="false">In!$F$119</definedName>
+    <definedName function="false" hidden="false" name="cqC_15_lo" vbProcedure="false">In!$D$119</definedName>
     <definedName function="false" hidden="false" name="cqC_16" vbProcedure="false">In!$E$120</definedName>
+    <definedName function="false" hidden="false" name="cqC_16_hi" vbProcedure="false">In!$F$120</definedName>
+    <definedName function="false" hidden="false" name="cqC_16_lo" vbProcedure="false">In!$D$120</definedName>
     <definedName function="false" hidden="false" name="cqC_17" vbProcedure="false">In!$E$121</definedName>
+    <definedName function="false" hidden="false" name="cqC_17_hi" vbProcedure="false">In!$F$121</definedName>
+    <definedName function="false" hidden="false" name="cqC_17_lo" vbProcedure="false">In!$D$121</definedName>
     <definedName function="false" hidden="false" name="cqC_18" vbProcedure="false">In!$E$122</definedName>
+    <definedName function="false" hidden="false" name="cqC_18_hi" vbProcedure="false">In!$F$122</definedName>
+    <definedName function="false" hidden="false" name="cqC_18_lo" vbProcedure="false">In!$D$122</definedName>
     <definedName function="false" hidden="false" name="cqC_19" vbProcedure="false">In!$E$123</definedName>
+    <definedName function="false" hidden="false" name="cqC_19_hi" vbProcedure="false">In!$F$123</definedName>
+    <definedName function="false" hidden="false" name="cqC_19_lo" vbProcedure="false">In!$D$123</definedName>
     <definedName function="false" hidden="false" name="cqC_8" vbProcedure="false">In!$E$112</definedName>
+    <definedName function="false" hidden="false" name="cqC_8_hi" vbProcedure="false">In!$F$112</definedName>
+    <definedName function="false" hidden="false" name="cqC_8_lo" vbProcedure="false">In!$D$112</definedName>
     <definedName function="false" hidden="false" name="cqC_9" vbProcedure="false">In!$E$113</definedName>
+    <definedName function="false" hidden="false" name="cqC_9_hi" vbProcedure="false">In!$F$113</definedName>
+    <definedName function="false" hidden="false" name="cqC_9_lo" vbProcedure="false">In!$D$113</definedName>
     <definedName function="false" hidden="false" name="cq_1" vbProcedure="false">In!$E$81</definedName>
     <definedName function="false" hidden="false" name="cq_2" vbProcedure="false">In!$E$82</definedName>
     <definedName function="false" hidden="false" name="cq_3" vbProcedure="false">In!$E$83</definedName>
@@ -126,8 +150,14 @@
     <definedName function="false" hidden="false" name="fx_hi" vbProcedure="false">In!$F$5</definedName>
     <definedName function="false" hidden="false" name="fx_lo" vbProcedure="false">In!$D$5</definedName>
     <definedName function="false" hidden="false" name="g_amd_26" vbProcedure="false">In!$E$195</definedName>
+    <definedName function="false" hidden="false" name="g_amd_26_hi" vbProcedure="false">In!$F$195</definedName>
+    <definedName function="false" hidden="false" name="g_amd_26_lo" vbProcedure="false">In!$D$195</definedName>
     <definedName function="false" hidden="false" name="g_amd_27" vbProcedure="false">In!$E$196</definedName>
+    <definedName function="false" hidden="false" name="g_amd_27_hi" vbProcedure="false">In!$F$196</definedName>
+    <definedName function="false" hidden="false" name="g_amd_27_lo" vbProcedure="false">In!$D$196</definedName>
     <definedName function="false" hidden="false" name="g_amd_28" vbProcedure="false">In!$E$197</definedName>
+    <definedName function="false" hidden="false" name="g_amd_28_hi" vbProcedure="false">In!$F$197</definedName>
+    <definedName function="false" hidden="false" name="g_amd_28_lo" vbProcedure="false">In!$D$197</definedName>
     <definedName function="false" hidden="false" name="g_bw_26" vbProcedure="false">In!$E$171</definedName>
     <definedName function="false" hidden="false" name="g_bw_27" vbProcedure="false">In!$E$172</definedName>
     <definedName function="false" hidden="false" name="g_bw_28" vbProcedure="false">In!$E$173</definedName>
@@ -135,8 +165,14 @@
     <definedName function="false" hidden="false" name="g_hp_27" vbProcedure="false">In!$E$190</definedName>
     <definedName function="false" hidden="false" name="g_hp_28" vbProcedure="false">In!$E$191</definedName>
     <definedName function="false" hidden="false" name="g_oth_26" vbProcedure="false">In!$E$213</definedName>
+    <definedName function="false" hidden="false" name="g_oth_26_hi" vbProcedure="false">In!$F$213</definedName>
+    <definedName function="false" hidden="false" name="g_oth_26_lo" vbProcedure="false">In!$D$213</definedName>
     <definedName function="false" hidden="false" name="g_oth_27" vbProcedure="false">In!$E$214</definedName>
+    <definedName function="false" hidden="false" name="g_oth_27_hi" vbProcedure="false">In!$F$214</definedName>
+    <definedName function="false" hidden="false" name="g_oth_27_lo" vbProcedure="false">In!$D$214</definedName>
     <definedName function="false" hidden="false" name="g_oth_28" vbProcedure="false">In!$E$215</definedName>
+    <definedName function="false" hidden="false" name="g_oth_28_hi" vbProcedure="false">In!$F$215</definedName>
+    <definedName function="false" hidden="false" name="g_oth_28_lo" vbProcedure="false">In!$D$215</definedName>
     <definedName function="false" hidden="false" name="g_rb_26" vbProcedure="false">In!$E$177</definedName>
     <definedName function="false" hidden="false" name="g_rb_27" vbProcedure="false">In!$E$178</definedName>
     <definedName function="false" hidden="false" name="g_rb_28" vbProcedure="false">In!$E$179</definedName>
@@ -147,8 +183,14 @@
     <definedName function="false" hidden="false" name="g_tpu_27" vbProcedure="false">In!$E$202</definedName>
     <definedName function="false" hidden="false" name="g_tpu_28" vbProcedure="false">In!$E$203</definedName>
     <definedName function="false" hidden="false" name="g_trn_26" vbProcedure="false">In!$E$207</definedName>
+    <definedName function="false" hidden="false" name="g_trn_26_hi" vbProcedure="false">In!$F$207</definedName>
+    <definedName function="false" hidden="false" name="g_trn_26_lo" vbProcedure="false">In!$D$207</definedName>
     <definedName function="false" hidden="false" name="g_trn_27" vbProcedure="false">In!$E$208</definedName>
+    <definedName function="false" hidden="false" name="g_trn_27_hi" vbProcedure="false">In!$F$208</definedName>
+    <definedName function="false" hidden="false" name="g_trn_27_lo" vbProcedure="false">In!$D$208</definedName>
     <definedName function="false" hidden="false" name="g_trn_28" vbProcedure="false">In!$E$209</definedName>
+    <definedName function="false" hidden="false" name="g_trn_28_hi" vbProcedure="false">In!$F$209</definedName>
+    <definedName function="false" hidden="false" name="g_trn_28_lo" vbProcedure="false">In!$D$209</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29" vbProcedure="false">In!$E$234</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29_hi" vbProcedure="false">In!$F$234</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29_lo" vbProcedure="false">In!$D$234</definedName>
@@ -242,17 +284,41 @@
     <definedName function="false" hidden="false" name="nqB_8" vbProcedure="false">In!$E$143</definedName>
     <definedName function="false" hidden="false" name="nqB_9" vbProcedure="false">In!$E$144</definedName>
     <definedName function="false" hidden="false" name="nqC_10" vbProcedure="false">In!$E$157</definedName>
+    <definedName function="false" hidden="false" name="nqC_10_hi" vbProcedure="false">In!$F$157</definedName>
+    <definedName function="false" hidden="false" name="nqC_10_lo" vbProcedure="false">In!$D$157</definedName>
     <definedName function="false" hidden="false" name="nqC_11" vbProcedure="false">In!$E$158</definedName>
+    <definedName function="false" hidden="false" name="nqC_11_hi" vbProcedure="false">In!$F$158</definedName>
+    <definedName function="false" hidden="false" name="nqC_11_lo" vbProcedure="false">In!$D$158</definedName>
     <definedName function="false" hidden="false" name="nqC_12" vbProcedure="false">In!$E$159</definedName>
+    <definedName function="false" hidden="false" name="nqC_12_hi" vbProcedure="false">In!$F$159</definedName>
+    <definedName function="false" hidden="false" name="nqC_12_lo" vbProcedure="false">In!$D$159</definedName>
     <definedName function="false" hidden="false" name="nqC_13" vbProcedure="false">In!$E$160</definedName>
+    <definedName function="false" hidden="false" name="nqC_13_hi" vbProcedure="false">In!$F$160</definedName>
+    <definedName function="false" hidden="false" name="nqC_13_lo" vbProcedure="false">In!$D$160</definedName>
     <definedName function="false" hidden="false" name="nqC_14" vbProcedure="false">In!$E$161</definedName>
+    <definedName function="false" hidden="false" name="nqC_14_hi" vbProcedure="false">In!$F$161</definedName>
+    <definedName function="false" hidden="false" name="nqC_14_lo" vbProcedure="false">In!$D$161</definedName>
     <definedName function="false" hidden="false" name="nqC_15" vbProcedure="false">In!$E$162</definedName>
+    <definedName function="false" hidden="false" name="nqC_15_hi" vbProcedure="false">In!$F$162</definedName>
+    <definedName function="false" hidden="false" name="nqC_15_lo" vbProcedure="false">In!$D$162</definedName>
     <definedName function="false" hidden="false" name="nqC_16" vbProcedure="false">In!$E$163</definedName>
+    <definedName function="false" hidden="false" name="nqC_16_hi" vbProcedure="false">In!$F$163</definedName>
+    <definedName function="false" hidden="false" name="nqC_16_lo" vbProcedure="false">In!$D$163</definedName>
     <definedName function="false" hidden="false" name="nqC_17" vbProcedure="false">In!$E$164</definedName>
+    <definedName function="false" hidden="false" name="nqC_17_hi" vbProcedure="false">In!$F$164</definedName>
+    <definedName function="false" hidden="false" name="nqC_17_lo" vbProcedure="false">In!$D$164</definedName>
     <definedName function="false" hidden="false" name="nqC_18" vbProcedure="false">In!$E$165</definedName>
+    <definedName function="false" hidden="false" name="nqC_18_hi" vbProcedure="false">In!$F$165</definedName>
+    <definedName function="false" hidden="false" name="nqC_18_lo" vbProcedure="false">In!$D$165</definedName>
     <definedName function="false" hidden="false" name="nqC_19" vbProcedure="false">In!$E$166</definedName>
+    <definedName function="false" hidden="false" name="nqC_19_hi" vbProcedure="false">In!$F$166</definedName>
+    <definedName function="false" hidden="false" name="nqC_19_lo" vbProcedure="false">In!$D$166</definedName>
     <definedName function="false" hidden="false" name="nqC_8" vbProcedure="false">In!$E$155</definedName>
+    <definedName function="false" hidden="false" name="nqC_8_hi" vbProcedure="false">In!$F$155</definedName>
+    <definedName function="false" hidden="false" name="nqC_8_lo" vbProcedure="false">In!$D$155</definedName>
     <definedName function="false" hidden="false" name="nqC_9" vbProcedure="false">In!$E$156</definedName>
+    <definedName function="false" hidden="false" name="nqC_9_hi" vbProcedure="false">In!$F$156</definedName>
+    <definedName function="false" hidden="false" name="nqC_9_lo" vbProcedure="false">In!$D$156</definedName>
     <definedName function="false" hidden="false" name="nq_1" vbProcedure="false">In!$E$124</definedName>
     <definedName function="false" hidden="false" name="nq_2" vbProcedure="false">In!$E$125</definedName>
     <definedName function="false" hidden="false" name="nq_3" vbProcedure="false">In!$E$126</definedName>
@@ -355,8 +421,14 @@
     <definedName function="false" hidden="false" name="um29_C_hi" vbProcedure="false">In!$F$222</definedName>
     <definedName function="false" hidden="false" name="um29_C_lo" vbProcedure="false">In!$D$222</definedName>
     <definedName function="false" hidden="false" name="u_amd_26" vbProcedure="false">In!$E$192</definedName>
+    <definedName function="false" hidden="false" name="u_amd_26_hi" vbProcedure="false">In!$F$192</definedName>
+    <definedName function="false" hidden="false" name="u_amd_26_lo" vbProcedure="false">In!$D$192</definedName>
     <definedName function="false" hidden="false" name="u_amd_27" vbProcedure="false">In!$E$193</definedName>
+    <definedName function="false" hidden="false" name="u_amd_27_hi" vbProcedure="false">In!$F$193</definedName>
+    <definedName function="false" hidden="false" name="u_amd_27_lo" vbProcedure="false">In!$D$193</definedName>
     <definedName function="false" hidden="false" name="u_amd_28" vbProcedure="false">In!$E$194</definedName>
+    <definedName function="false" hidden="false" name="u_amd_28_hi" vbProcedure="false">In!$F$194</definedName>
+    <definedName function="false" hidden="false" name="u_amd_28_lo" vbProcedure="false">In!$D$194</definedName>
     <definedName function="false" hidden="false" name="u_bw_26" vbProcedure="false">In!$E$168</definedName>
     <definedName function="false" hidden="false" name="u_bw_27" vbProcedure="false">In!$E$169</definedName>
     <definedName function="false" hidden="false" name="u_bw_28" vbProcedure="false">In!$E$170</definedName>
@@ -364,20 +436,38 @@
     <definedName function="false" hidden="false" name="u_hp_27" vbProcedure="false">In!$E$187</definedName>
     <definedName function="false" hidden="false" name="u_hp_28" vbProcedure="false">In!$E$188</definedName>
     <definedName function="false" hidden="false" name="u_oth_26" vbProcedure="false">In!$E$210</definedName>
+    <definedName function="false" hidden="false" name="u_oth_26_hi" vbProcedure="false">In!$F$210</definedName>
+    <definedName function="false" hidden="false" name="u_oth_26_lo" vbProcedure="false">In!$D$210</definedName>
     <definedName function="false" hidden="false" name="u_oth_27" vbProcedure="false">In!$E$211</definedName>
+    <definedName function="false" hidden="false" name="u_oth_27_hi" vbProcedure="false">In!$F$211</definedName>
+    <definedName function="false" hidden="false" name="u_oth_27_lo" vbProcedure="false">In!$D$211</definedName>
     <definedName function="false" hidden="false" name="u_oth_28" vbProcedure="false">In!$E$212</definedName>
+    <definedName function="false" hidden="false" name="u_oth_28_hi" vbProcedure="false">In!$F$212</definedName>
+    <definedName function="false" hidden="false" name="u_oth_28_lo" vbProcedure="false">In!$D$212</definedName>
     <definedName function="false" hidden="false" name="u_rb_26" vbProcedure="false">In!$E$174</definedName>
     <definedName function="false" hidden="false" name="u_rb_27" vbProcedure="false">In!$E$175</definedName>
     <definedName function="false" hidden="false" name="u_rb_28" vbProcedure="false">In!$E$176</definedName>
     <definedName function="false" hidden="false" name="u_ru_26" vbProcedure="false">In!$E$180</definedName>
+    <definedName function="false" hidden="false" name="u_ru_26_hi" vbProcedure="false">In!$F$180</definedName>
+    <definedName function="false" hidden="false" name="u_ru_26_lo" vbProcedure="false">In!$D$180</definedName>
     <definedName function="false" hidden="false" name="u_ru_27" vbProcedure="false">In!$E$181</definedName>
+    <definedName function="false" hidden="false" name="u_ru_27_hi" vbProcedure="false">In!$F$181</definedName>
+    <definedName function="false" hidden="false" name="u_ru_27_lo" vbProcedure="false">In!$D$181</definedName>
     <definedName function="false" hidden="false" name="u_ru_28" vbProcedure="false">In!$E$182</definedName>
+    <definedName function="false" hidden="false" name="u_ru_28_hi" vbProcedure="false">In!$F$182</definedName>
+    <definedName function="false" hidden="false" name="u_ru_28_lo" vbProcedure="false">In!$D$182</definedName>
     <definedName function="false" hidden="false" name="u_tpu_26" vbProcedure="false">In!$E$198</definedName>
     <definedName function="false" hidden="false" name="u_tpu_27" vbProcedure="false">In!$E$199</definedName>
     <definedName function="false" hidden="false" name="u_tpu_28" vbProcedure="false">In!$E$200</definedName>
     <definedName function="false" hidden="false" name="u_trn_26" vbProcedure="false">In!$E$204</definedName>
+    <definedName function="false" hidden="false" name="u_trn_26_hi" vbProcedure="false">In!$F$204</definedName>
+    <definedName function="false" hidden="false" name="u_trn_26_lo" vbProcedure="false">In!$D$204</definedName>
     <definedName function="false" hidden="false" name="u_trn_27" vbProcedure="false">In!$E$205</definedName>
+    <definedName function="false" hidden="false" name="u_trn_27_hi" vbProcedure="false">In!$F$205</definedName>
+    <definedName function="false" hidden="false" name="u_trn_27_lo" vbProcedure="false">In!$D$205</definedName>
     <definedName function="false" hidden="false" name="u_trn_28" vbProcedure="false">In!$E$206</definedName>
+    <definedName function="false" hidden="false" name="u_trn_28_hi" vbProcedure="false">In!$F$206</definedName>
+    <definedName function="false" hidden="false" name="u_trn_28_lo" vbProcedure="false">In!$D$206</definedName>
     <definedName function="false" hidden="false" name="w_c" vbProcedure="false">In!$E$31</definedName>
     <definedName function="false" hidden="false" name="w_h" vbProcedure="false">In!$E$32</definedName>
     <definedName function="false" hidden="false" name="w_n" vbProcedure="false">In!$E$33</definedName>
@@ -392,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="1080">
   <si>
     <r>
       <rPr>
@@ -10653,7 +10743,121 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">自谷底回升</t>
+      <t xml:space="preserve">自谷底回升。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±5pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028–29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，表示路徑形狀的不確定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不是另一個情境</t>
     </r>
   </si>
   <si>
@@ -13535,7 +13739,121 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年水準</t>
+      <t xml:space="preserve">年水準。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±5pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028–29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，表示路徑形狀的不確定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不是另一個情境</t>
     </r>
   </si>
   <si>
@@ -15338,7 +15656,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">／封裝</t>
+      <t xml:space="preserve">／封裝。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 0–0.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 1.0–3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：時程提前／延後一年）</t>
     </r>
   </si>
   <si>
@@ -15444,6 +15838,122 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NVIDIA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin Ultra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每封裝 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 TB HBM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（產品路線圖，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">標記由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interested-party</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：規格為公司公布，不是假設）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">g_ru_27</t>
   </si>
   <si>
@@ -15993,6 +16503,148 @@
       </rPr>
       <t xml:space="preserve">Assumed</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 0.6–0.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 1.2–1.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 1.5–2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MI355X 288</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MI450 432 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為上下限</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">u_amd_27</t>
@@ -16605,6 +17257,167 @@
       </rPr>
       <t xml:space="preserve">Trn3 144</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 1.5–2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 2.0–3.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 2.0–4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trn2 96</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trn3 144</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、下一代 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">256 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為界</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">u_trn_27</t>
@@ -16936,6 +17749,101 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">JPMorgan ASIC 12.5M − TPU − Trainium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 0.5–1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 3.0–6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 3.5–7.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM ±50 GB</t>
     </r>
   </si>
   <si>
@@ -17833,7 +18741,178 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">測試機需求用同一組係數</t>
+      <t xml:space="preserve">測試機需求用同一組係數。情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為定義值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">標記由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仍為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -19536,6 +20615,84 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無外部預測；供給新廠（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、龍仁、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M15X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）投產下單價緩降</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">hbm_p29_B</t>
   </si>
   <si>
@@ -19595,6 +20752,65 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無外部預測；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已下修後持平</t>
     </r>
   </si>
   <si>
@@ -36033,24 +37249,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
         <v>4.46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -36062,34 +37278,34 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
         <v>55 ／ 154</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
         <v>1.23255275</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>166</v>
@@ -36120,31 +37336,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36152,87 +37368,87 @@
         <v>214</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
     </row>
   </sheetData>
@@ -38510,8 +39726,14 @@
       <c r="C112" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D112" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E112" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>63</v>
@@ -38530,8 +39752,14 @@
       <c r="C113" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D113" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E113" s="7" t="n">
         <v>0.02</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>0.07</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>63</v>
@@ -38550,8 +39778,14 @@
       <c r="C114" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D114" s="7" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="E114" s="7" t="n">
         <v>-0.08</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G114" s="8" t="s">
         <v>63</v>
@@ -38570,8 +39804,14 @@
       <c r="C115" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D115" s="7" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="E115" s="7" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G115" s="8" t="s">
         <v>63</v>
@@ -38590,8 +39830,14 @@
       <c r="C116" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D116" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E116" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G116" s="8" t="s">
         <v>63</v>
@@ -38610,8 +39856,14 @@
       <c r="C117" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D117" s="7" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="E117" s="7" t="n">
         <v>-0.3</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>-0.2</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>63</v>
@@ -38630,8 +39882,14 @@
       <c r="C118" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D118" s="7" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="E118" s="7" t="n">
         <v>-0.25</v>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>63</v>
@@ -38650,8 +39908,14 @@
       <c r="C119" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D119" s="7" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="E119" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>63</v>
@@ -38670,8 +39934,14 @@
       <c r="C120" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D120" s="7" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="E120" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>63</v>
@@ -38690,8 +39960,14 @@
       <c r="C121" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D121" s="7" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E121" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>0.15</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>63</v>
@@ -38710,8 +39986,14 @@
       <c r="C122" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D122" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E122" s="7" t="n">
         <v>0.08</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>0.18</v>
       </c>
       <c r="G122" s="8" t="s">
         <v>63</v>
@@ -38730,8 +40012,14 @@
       <c r="C123" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D123" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E123" s="7" t="n">
         <v>0.1</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>0.2</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>63</v>
@@ -39370,8 +40658,14 @@
       <c r="C155" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D155" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E155" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G155" s="8" t="s">
         <v>63</v>
@@ -39390,8 +40684,14 @@
       <c r="C156" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D156" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E156" s="7" t="n">
         <v>0.02</v>
+      </c>
+      <c r="F156" s="7" t="n">
+        <v>0.07</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>63</v>
@@ -39410,8 +40710,14 @@
       <c r="C157" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D157" s="7" t="n">
+        <v>-0.15</v>
+      </c>
       <c r="E157" s="7" t="n">
         <v>-0.1</v>
+      </c>
+      <c r="F157" s="7" t="n">
+        <v>-0.05</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>63</v>
@@ -39430,8 +40736,14 @@
       <c r="C158" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D158" s="7" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="E158" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F158" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G158" s="8" t="s">
         <v>63</v>
@@ -39450,8 +40762,14 @@
       <c r="C159" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D159" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E159" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F159" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>63</v>
@@ -39470,8 +40788,14 @@
       <c r="C160" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D160" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E160" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F160" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>63</v>
@@ -39490,8 +40814,14 @@
       <c r="C161" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D161" s="7" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="E161" s="7" t="n">
         <v>-0.25</v>
+      </c>
+      <c r="F161" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>63</v>
@@ -39510,8 +40840,14 @@
       <c r="C162" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D162" s="7" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="E162" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>63</v>
@@ -39530,8 +40866,14 @@
       <c r="C163" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D163" s="7" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="E163" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="F163" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>63</v>
@@ -39550,8 +40892,14 @@
       <c r="C164" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D164" s="7" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E164" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F164" s="7" t="n">
+        <v>0.15</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>63</v>
@@ -39570,8 +40918,14 @@
       <c r="C165" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D165" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E165" s="7" t="n">
         <v>0.08</v>
+      </c>
+      <c r="F165" s="7" t="n">
+        <v>0.18</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>63</v>
@@ -39590,8 +40944,14 @@
       <c r="C166" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D166" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E166" s="7" t="n">
         <v>0.1</v>
+      </c>
+      <c r="F166" s="7" t="n">
+        <v>0.2</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>63</v>
@@ -39855,7 +41215,13 @@
       <c r="C180" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D180" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E180" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G180" s="8" t="s">
@@ -39875,8 +41241,14 @@
       <c r="C181" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D181" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E181" s="7" t="n">
         <v>0.3</v>
+      </c>
+      <c r="F181" s="7" t="n">
+        <v>0.6</v>
       </c>
       <c r="G181" s="8" t="s">
         <v>63</v>
@@ -39895,8 +41267,14 @@
       <c r="C182" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D182" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="E182" s="7" t="n">
         <v>2</v>
+      </c>
+      <c r="F182" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>63</v>
@@ -39919,18 +41297,18 @@
         <v>1024</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H183" s="5" t="s">
-        <v>99</v>
+        <v>59</v>
+      </c>
+      <c r="H183" s="8" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C184" s="0" t="s">
         <v>433</v>
@@ -39939,7 +41317,7 @@
         <v>1024</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H184" s="5" t="s">
         <v>99</v>
@@ -39947,10 +41325,10 @@
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C185" s="0" t="s">
         <v>433</v>
@@ -39959,7 +41337,7 @@
         <v>1024</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H185" s="5" t="s">
         <v>99</v>
@@ -39967,10 +41345,10 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>425</v>
@@ -39982,15 +41360,15 @@
         <v>59</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>425</v>
@@ -40007,10 +41385,10 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>425</v>
@@ -40027,10 +41405,10 @@
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C189" s="0" t="s">
         <v>433</v>
@@ -40047,10 +41425,10 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C190" s="0" t="s">
         <v>433</v>
@@ -40067,10 +41445,10 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C191" s="0" t="s">
         <v>433</v>
@@ -40087,39 +41465,51 @@
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D192" s="7" t="n">
+        <v>0.6</v>
+      </c>
       <c r="E192" s="7" t="n">
         <v>0.75</v>
       </c>
+      <c r="F192" s="7" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G192" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D193" s="7" t="n">
+        <v>1.2</v>
+      </c>
       <c r="E193" s="7" t="n">
         <v>1.5</v>
       </c>
+      <c r="F193" s="7" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G193" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H193" s="5" t="s">
         <v>99</v>
@@ -40127,19 +41517,25 @@
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D194" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E194" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F194" s="7" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G194" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H194" s="5" t="s">
         <v>99</v>
@@ -40147,19 +41543,25 @@
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C195" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D195" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="E195" s="7" t="n">
         <v>288</v>
       </c>
+      <c r="F195" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="G195" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H195" s="5" t="s">
         <v>99</v>
@@ -40167,19 +41569,25 @@
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C196" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D196" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="E196" s="7" t="n">
         <v>360</v>
       </c>
+      <c r="F196" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="G196" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H196" s="5" t="s">
         <v>99</v>
@@ -40187,19 +41595,25 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C197" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D197" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="E197" s="7" t="n">
         <v>432</v>
       </c>
+      <c r="F197" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="G197" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H197" s="5" t="s">
         <v>99</v>
@@ -40207,10 +41621,10 @@
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>425</v>
@@ -40222,15 +41636,15 @@
         <v>59</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>425</v>
@@ -40247,10 +41661,10 @@
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>425</v>
@@ -40267,10 +41681,10 @@
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C201" s="0" t="s">
         <v>433</v>
@@ -40287,10 +41701,10 @@
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C202" s="0" t="s">
         <v>433</v>
@@ -40307,10 +41721,10 @@
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C203" s="0" t="s">
         <v>433</v>
@@ -40327,37 +41741,49 @@
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C204" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D204" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E204" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F204" s="7" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G204" s="8" t="s">
         <v>63</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D205" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="E205" s="7" t="n">
         <v>2.5</v>
       </c>
+      <c r="F205" s="7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G205" s="8" t="s">
         <v>63</v>
       </c>
@@ -40367,17 +41793,23 @@
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D206" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="E206" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="F206" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="G206" s="8" t="s">
         <v>63</v>
       </c>
@@ -40387,17 +41819,23 @@
     </row>
     <row r="207" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C207" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D207" s="7" t="n">
+        <v>96</v>
+      </c>
       <c r="E207" s="7" t="n">
         <v>110</v>
       </c>
+      <c r="F207" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="G207" s="8" t="s">
         <v>63</v>
       </c>
@@ -40407,17 +41845,23 @@
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C208" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D208" s="7" t="n">
+        <v>120</v>
+      </c>
       <c r="E208" s="7" t="n">
         <v>144</v>
       </c>
+      <c r="F208" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="G208" s="8" t="s">
         <v>63</v>
       </c>
@@ -40427,17 +41871,23 @@
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C209" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D209" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="E209" s="7" t="n">
         <v>200</v>
       </c>
+      <c r="F209" s="7" t="n">
+        <v>256</v>
+      </c>
       <c r="G209" s="8" t="s">
         <v>63</v>
       </c>
@@ -40447,39 +41897,51 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D210" s="7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E210" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="F210" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G210" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D211" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="E211" s="7" t="n">
         <v>4.5</v>
       </c>
+      <c r="F211" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="G211" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H211" s="5" t="s">
         <v>99</v>
@@ -40487,19 +41949,25 @@
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>425</v>
       </c>
+      <c r="D212" s="7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="E212" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="F212" s="7" t="n">
+        <v>7</v>
+      </c>
       <c r="G212" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H212" s="5" t="s">
         <v>99</v>
@@ -40507,19 +41975,25 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C213" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D213" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="E213" s="7" t="n">
         <v>150</v>
       </c>
+      <c r="F213" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="G213" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H213" s="5" t="s">
         <v>99</v>
@@ -40527,19 +42001,25 @@
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C214" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D214" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="E214" s="7" t="n">
         <v>200</v>
       </c>
+      <c r="F214" s="7" t="n">
+        <v>250</v>
+      </c>
       <c r="G214" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H214" s="5" t="s">
         <v>99</v>
@@ -40547,19 +42027,25 @@
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C215" s="0" t="s">
         <v>433</v>
       </c>
+      <c r="D215" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="E215" s="7" t="n">
         <v>250</v>
       </c>
+      <c r="F215" s="7" t="n">
+        <v>300</v>
+      </c>
       <c r="G215" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H215" s="5" t="s">
         <v>99</v>
@@ -40567,15 +42053,15 @@
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>226</v>
@@ -40584,18 +42070,18 @@
         <v>1</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C218" s="0" t="s">
         <v>226</v>
@@ -40604,7 +42090,7 @@
         <v>1</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="H218" s="5" t="s">
         <v>99</v>
@@ -40612,10 +42098,10 @@
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C219" s="0" t="s">
         <v>226</v>
@@ -40638,10 +42124,10 @@
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>226</v>
@@ -40664,10 +42150,10 @@
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>226</v>
@@ -40690,10 +42176,10 @@
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>226</v>
@@ -40716,18 +42202,18 @@
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D224" s="7" t="n">
         <v>34</v>
@@ -40742,15 +42228,15 @@
         <v>44</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>49</v>
@@ -40768,15 +42254,15 @@
         <v>59</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>226</v>
@@ -40794,15 +42280,15 @@
         <v>63</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>49</v>
@@ -40820,15 +42306,15 @@
         <v>59</v>
       </c>
       <c r="H227" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>49</v>
@@ -40846,18 +42332,18 @@
         <v>63</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D229" s="7" t="n">
         <v>12.5</v>
@@ -40872,15 +42358,15 @@
         <v>59</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>49</v>
@@ -40898,15 +42384,15 @@
         <v>59</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C231" s="0" t="s">
         <v>49</v>
@@ -40924,15 +42410,15 @@
         <v>59</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>49</v>
@@ -40950,15 +42436,15 @@
         <v>63</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>49</v>
@@ -40976,15 +42462,15 @@
         <v>63</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>49</v>
@@ -41002,15 +42488,15 @@
         <v>63</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C235" s="0" t="s">
         <v>49</v>
@@ -41028,15 +42514,15 @@
         <v>63</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>49</v>
@@ -41053,13 +42539,16 @@
       <c r="G236" s="8" t="s">
         <v>63</v>
       </c>
+      <c r="H236" s="8" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C237" s="0" t="s">
         <v>49</v>
@@ -41076,13 +42565,16 @@
       <c r="G237" s="8" t="s">
         <v>63</v>
       </c>
+      <c r="H237" s="8" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C238" s="0" t="s">
         <v>49</v>
@@ -41100,23 +42592,23 @@
         <v>63</v>
       </c>
       <c r="H238" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D240" s="7" t="n">
         <v>340</v>
@@ -41128,21 +42620,21 @@
         <v>400</v>
       </c>
       <c r="G240" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D241" s="7" t="n">
         <v>38</v>
@@ -41157,18 +42649,18 @@
         <v>39</v>
       </c>
       <c r="H241" s="8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B242" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="C242" s="0" t="s">
         <v>601</v>
-      </c>
-      <c r="C242" s="0" t="s">
-        <v>598</v>
       </c>
       <c r="D242" s="7" t="n">
         <v>3.5</v>
@@ -41183,18 +42675,18 @@
         <v>39</v>
       </c>
       <c r="H242" s="8" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E243" s="7" t="n">
         <v>54.6</v>
@@ -41203,18 +42695,18 @@
         <v>59</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E244" s="7" t="n">
         <v>77.4</v>
@@ -41223,18 +42715,18 @@
         <v>59</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E245" s="7" t="n">
         <v>152.8</v>
@@ -41243,20 +42735,20 @@
         <v>59</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C247" s="9" t="s">
         <v>49</v>
@@ -41270,15 +42762,15 @@
         <v>63</v>
       </c>
       <c r="H247" s="9" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C248" s="9" t="s">
         <v>49</v>
@@ -41292,15 +42784,15 @@
         <v>63</v>
       </c>
       <c r="H248" s="9" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C249" s="9" t="s">
         <v>49</v>
@@ -41314,15 +42806,15 @@
         <v>63</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C250" s="9" t="s">
         <v>49</v>
@@ -41336,15 +42828,15 @@
         <v>63</v>
       </c>
       <c r="H250" s="9" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C251" s="9" t="s">
         <v>49</v>
@@ -41358,15 +42850,15 @@
         <v>63</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>49</v>
@@ -41381,15 +42873,15 @@
         <v>39</v>
       </c>
       <c r="H252" s="9" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C253" s="9" t="s">
         <v>49</v>
@@ -41403,15 +42895,15 @@
         <v>63</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C254" s="9" t="s">
         <v>49</v>
@@ -41426,15 +42918,15 @@
         <v>39</v>
       </c>
       <c r="H254" s="9" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C255" s="9" t="s">
         <v>49</v>
@@ -41449,15 +42941,15 @@
         <v>63</v>
       </c>
       <c r="H255" s="10" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C256" s="9" t="s">
         <v>49</v>
@@ -41472,15 +42964,15 @@
         <v>63</v>
       </c>
       <c r="H256" s="10" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="9" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C257" s="9" t="s">
         <v>49</v>
@@ -41495,15 +42987,15 @@
         <v>63</v>
       </c>
       <c r="H257" s="10" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C258" s="9" t="s">
         <v>226</v>
@@ -41517,15 +43009,15 @@
         <v>63</v>
       </c>
       <c r="H258" s="9" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="9" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C259" s="9" t="s">
         <v>226</v>
@@ -41539,15 +43031,15 @@
         <v>63</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="9" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C260" s="9" t="s">
         <v>49</v>
@@ -41562,15 +43054,15 @@
         <v>39</v>
       </c>
       <c r="H260" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="9" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C261" s="9" t="s">
         <v>49</v>
@@ -41585,15 +43077,15 @@
         <v>39</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="9" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C262" s="9" t="s">
         <v>49</v>
@@ -41608,15 +43100,15 @@
         <v>39</v>
       </c>
       <c r="H262" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="9" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C263" s="9" t="s">
         <v>43</v>
@@ -41634,15 +43126,15 @@
         <v>59</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="9" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C264" s="9" t="s">
         <v>43</v>
@@ -41656,15 +43148,15 @@
         <v>59</v>
       </c>
       <c r="H264" s="9" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="9" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C265" s="9" t="s">
         <v>43</v>
@@ -41678,15 +43170,15 @@
         <v>59</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="9" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C266" s="9" t="s">
         <v>43</v>
@@ -41700,7 +43192,7 @@
         <v>59</v>
       </c>
       <c r="H266" s="9" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>
@@ -41728,83 +43220,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="V3" s="13" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
@@ -41888,10 +43380,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
@@ -41975,10 +43467,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
@@ -42062,10 +43554,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>695</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>692</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>689</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
@@ -42149,10 +43641,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
@@ -42236,10 +43728,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
@@ -42323,50 +43815,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">AVERAGE(C4:F4)</f>
@@ -42407,10 +43899,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">AVERAGE(C5:F5)</f>
@@ -42451,10 +43943,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">AVERAGE(C6:F6)</f>
@@ -42495,10 +43987,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>695</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>692</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>689</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">AVERAGE(C8:F8)</f>
@@ -42539,10 +44031,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">AVERAGE(C9:F9)</f>
@@ -42583,10 +44075,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">AVERAGE(C10:F10)</f>
@@ -42651,7 +44143,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42662,35 +44154,35 @@
         <v>29</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">u_bw_26*g_bw_26</f>
@@ -42707,10 +44199,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">u_rb_26*g_rb_26</f>
@@ -42727,10 +44219,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">u_ru_26*g_ru_26</f>
@@ -42747,10 +44239,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>710</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>707</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">u_hp_26*g_hp_26</f>
@@ -42767,10 +44259,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">u_amd_26*g_amd_26</f>
@@ -42787,10 +44279,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">u_tpu_26*g_tpu_26</f>
@@ -42807,10 +44299,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">u_trn_26*g_trn_26</f>
@@ -42827,10 +44319,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">u_oth_26*g_oth_26</f>
@@ -42847,10 +44339,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">SUM(D5:D12)/1000</f>
@@ -42871,10 +44363,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D13*hbm_gross</f>
@@ -42895,7 +44387,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>425</v>
@@ -42913,12 +44405,12 @@
         <v>26.5</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>433</v>
@@ -42938,10 +44430,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">D17/(1+hbm_g26)</f>
@@ -42964,12 +44456,12 @@
         <v>11.477169466875</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>226</v>
@@ -42989,12 +44481,12 @@
         <v>1</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>226</v>
@@ -43014,12 +44506,12 @@
         <v>0.85</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>226</v>
@@ -43039,15 +44531,15 @@
         <v>0.6</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">D14*D18</f>
@@ -43068,10 +44560,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">D14*D19</f>
@@ -43092,10 +44584,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">D14*D20</f>
@@ -43116,10 +44608,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">C17</f>
@@ -43142,15 +44634,15 @@
         <v>11.477169466875</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">C17</f>
@@ -43175,10 +44667,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">C17</f>
@@ -43203,10 +44695,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D27" s="14" t="n">
         <f aca="false">D21-D17</f>
@@ -43227,10 +44719,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">D22-D17</f>
@@ -43251,10 +44743,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">D23-D17</f>
@@ -43275,10 +44767,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C30" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -43303,10 +44795,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -43331,10 +44823,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -43359,10 +44851,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">C24*C30</f>
@@ -43387,10 +44879,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">C25*C31</f>
@@ -43415,10 +44907,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">C26*C32</f>
@@ -43443,15 +44935,15 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">(D5+D6+D7+D8)/1000*hbm_p26</f>
@@ -43460,22 +44952,22 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">nv_dc26*nv_hbm/nv_content</f>
         <v>38.9728971962617</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>49</v>
@@ -43487,7 +44979,7 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>425</v>
@@ -43501,15 +44993,15 @@
         <v>7.6</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">pub26_lo</f>
@@ -43526,7 +45018,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>49</v>
@@ -43565,7 +45057,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43573,36 +45065,36 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>17.639</v>
@@ -43637,7 +45129,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">F4*0.773</f>
@@ -43662,7 +45154,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F6" s="14" t="n">
         <f aca="false">F4*0.22</f>
@@ -43687,7 +45179,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">F4-F5-F6</f>
@@ -43712,7 +45204,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">F4*(1-0.79)</f>
@@ -43737,7 +45229,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">F4-F8-F10</f>
@@ -43762,7 +45254,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>7.441</v>
@@ -43797,7 +45289,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IF(B4=0,"",B10/B4)</f>
@@ -43838,7 +45330,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>8.108</v>
@@ -43873,7 +45365,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>3.334</v>
@@ -43908,7 +45400,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="G14" s="0" t="n">
         <v>1</v>
@@ -43924,7 +45416,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>1</v>
@@ -43940,7 +45432,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -43969,12 +45461,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43982,72 +45474,72 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">SUM(Q!B4:E4)</f>
@@ -44096,7 +45588,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">Q!J5-C6</f>
@@ -44139,12 +45631,12 @@
         <v>99.342377931568</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">(Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26)*fx/1000</f>
@@ -44187,12 +45679,12 @@
         <v>75.3957801559872</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">Q!J6</f>
@@ -44237,7 +45729,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">Q!J7</f>
@@ -44282,7 +45774,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">C6/C4</f>
@@ -44327,7 +45819,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUM(Q!B13:E13)</f>
@@ -44376,7 +45868,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">w_c*(1+cb_1)+w_h*D31/C31+w_n*(1+nb_1)</f>
@@ -44417,7 +45909,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">Q!J8</f>
@@ -44460,12 +45952,12 @@
         <v>79.3034449351957</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">Q!J9</f>
@@ -44510,7 +46002,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">SUM(Q!B10:E10)</f>
@@ -44559,7 +46051,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B14/B4</f>
@@ -44608,7 +46100,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">nm_rev_0</f>
@@ -44653,7 +46145,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">nm_op_0</f>
@@ -44698,7 +46190,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C4+C16</f>
@@ -44777,12 +46269,12 @@
         <v>216.483583576036</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C14+C17</f>
@@ -44827,7 +46319,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">SUM(Q!B12:E12)</f>
@@ -44910,12 +46402,12 @@
         <v>32.3783962634274</v>
       </c>
       <c r="V20" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">cap_0</f>
@@ -44960,7 +46452,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">C20+C10-C21</f>
@@ -45005,7 +46497,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">div_0</f>
@@ -45050,7 +46542,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">bb_0</f>
@@ -45093,12 +46585,12 @@
         <v>28.3807982239078</v>
       </c>
       <c r="V24" s="5" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">eq_last+(Q!H12+Q!I12)+extra_eq-C24-C23</f>
@@ -45143,7 +46635,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">nc_last+(Q!H12+Q!I12)+(Q!H13+Q!I13)-capex_rem+extra_eq-C24-C23</f>
@@ -45188,7 +46680,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">sh_last+extra_sh-bb_sh_0</f>
@@ -45269,7 +46761,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">C25/C27*1000000</f>
@@ -45314,7 +46806,7 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">C20/C27*1000000</f>
@@ -45395,7 +46887,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">C20/C25</f>
@@ -45440,7 +46932,7 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">(Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26)</f>
@@ -45485,7 +46977,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">D18/C18-1</f>
@@ -45562,7 +47054,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">C20/C18</f>
@@ -45671,30 +47163,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45706,10 +47198,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E4" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45726,17 +47218,17 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E5" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45753,17 +47245,17 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45787,10 +47279,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -45807,17 +47299,17 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E8" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -45834,17 +47326,17 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -45868,10 +47360,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -45888,17 +47380,17 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -45915,17 +47407,17 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -45949,10 +47441,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E13" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -45969,17 +47461,17 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E14" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -45996,17 +47488,17 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E15" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -46030,10 +47522,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E16" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -46050,17 +47542,17 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E17" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -46077,17 +47569,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E18" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -46111,10 +47603,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E19" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -46131,17 +47623,17 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E20" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -46158,17 +47650,17 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E21" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -46192,10 +47684,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E22" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -46212,17 +47704,17 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E23" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -46239,17 +47731,17 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E24" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -46273,10 +47765,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E25" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -46293,17 +47785,17 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E26" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -46320,17 +47812,17 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E27" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -46354,10 +47846,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E28" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46374,17 +47866,17 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B29" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46401,17 +47893,17 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E30" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46435,10 +47927,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E31" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46455,17 +47947,17 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E32" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46482,17 +47974,17 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E33" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46516,10 +48008,10 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E34" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46543,10 +48035,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E35" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46570,10 +48062,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E36" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46597,10 +48089,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E37" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46624,10 +48116,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E38" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46651,10 +48143,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E39" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46678,10 +48170,10 @@
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E40" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46705,10 +48197,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E41" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46732,10 +48224,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E42" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46759,10 +48251,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E43" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -46786,10 +48278,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E44" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -46813,10 +48305,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E45" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -46840,10 +48332,10 @@
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E46" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -46867,10 +48359,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E47" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -46894,10 +48386,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E48" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -46921,10 +48413,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E49" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -46948,10 +48440,10 @@
         <v>8</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -46975,10 +48467,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E51" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -47002,10 +48494,10 @@
         <v>4</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E52" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -47029,10 +48521,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E53" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -47056,10 +48548,10 @@
         <v>12</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E54" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -47083,10 +48575,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E55" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -47110,10 +48602,10 @@
         <v>8</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E56" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -47137,10 +48629,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E57" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -47164,10 +48656,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E58" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -47191,10 +48683,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E59" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -47218,10 +48710,10 @@
         <v>12</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E60" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -47238,36 +48730,36 @@
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B68" s="18" t="n">
         <v>1.31</v>
@@ -47276,12 +48768,12 @@
         <v>1.35</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B69" s="18" t="n">
         <v>1.59</v>
@@ -47290,12 +48782,12 @@
         <v>1.6</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B70" s="18" t="n">
         <v>0.8832</v>
@@ -47306,7 +48798,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B71" s="18" t="n">
         <v>1.34</v>
@@ -47317,7 +48809,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B72" s="18" t="n">
         <v>1.56</v>
@@ -47328,7 +48820,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B73" s="18" t="n">
         <v>1.45</v>
@@ -47339,7 +48831,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B74" s="18" t="n">
         <v>0.81</v>
@@ -47350,7 +48842,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B75" s="18" t="n">
         <v>1.87</v>
@@ -47361,7 +48853,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B76" s="18" t="n">
         <v>1.62</v>
@@ -47372,7 +48864,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B77" s="18" t="n">
         <v>3.86</v>
@@ -47380,7 +48872,7 @@
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B78" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.25)</f>
@@ -47393,7 +48885,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B79" s="14" t="n">
         <f aca="false">MEDIAN(B68:B77)</f>
@@ -47406,7 +48898,7 @@
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B80" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.75)</f>
@@ -47419,7 +48911,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B81" s="14" t="n">
         <f aca="false">MIN(B68:B77)</f>
@@ -47432,7 +48924,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B82" s="14" t="n">
         <f aca="false">MAX(B68:B77)</f>
@@ -47445,7 +48937,7 @@
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B83" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B78,C78),2)</f>
@@ -47454,7 +48946,7 @@
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B84" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B79,C79),2)</f>
@@ -47463,7 +48955,7 @@
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B85" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B80,C80),2)</f>
@@ -47472,7 +48964,7 @@
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B86" s="14" t="n">
         <f aca="false">ROUND(MIN(B81,C81),2)</f>
@@ -47481,7 +48973,7 @@
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B87" s="14" t="n">
         <f aca="false">ROUND(MAX(B82,C82),2)</f>
@@ -47490,48 +48982,48 @@
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C91" s="14" t="n">
         <f aca="false">B83</f>
         <v>1.33</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E91" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47552,17 +49044,17 @@
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C92" s="14" t="n">
         <f aca="false">B84</f>
         <v>1.48</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="E92" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47583,17 +49075,17 @@
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C93" s="14" t="n">
         <f aca="false">B85</f>
         <v>1.61</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="E93" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -47614,29 +49106,29 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B98" s="18" t="n">
         <v>9.57</v>
@@ -47646,12 +49138,12 @@
         <v>9.57</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B99" s="18" t="n">
         <v>4.61</v>
@@ -47661,12 +49153,12 @@
         <v>4.61</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B100" s="18" t="n">
         <v>2.54</v>
@@ -47676,12 +49168,12 @@
         <v>2.54</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B101" s="18" t="n">
         <v>30.2</v>
@@ -47691,12 +49183,12 @@
         <v>30.2</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B102" s="18" t="n">
         <v>16.2</v>
@@ -47708,7 +49200,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B103" s="18" t="n">
         <v>9.01</v>
@@ -47723,7 +49215,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B104" s="18" t="n">
         <v>22.6</v>
@@ -47738,7 +49230,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B105" s="18" t="n">
         <v>-10.6</v>
@@ -47750,7 +49242,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B106" s="18" t="n">
         <v>5.99</v>
@@ -47765,7 +49257,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B107" s="18" t="n">
         <v>10.5</v>
@@ -47780,7 +49272,7 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B108" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.25)</f>
@@ -47797,7 +49289,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B109" s="14" t="n">
         <f aca="false">MEDIAN(B98:B107)</f>
@@ -47814,7 +49306,7 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B110" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.75)</f>
@@ -47831,7 +49323,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B111" s="14" t="n">
         <f aca="false">MIN(B98:B107)</f>
@@ -47848,7 +49340,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B112" s="14" t="n">
         <f aca="false">MAX(B98:B107)</f>
@@ -47865,7 +49357,7 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B113" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(C108),2)</f>
@@ -47874,7 +49366,7 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B114" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(C109),2)</f>
@@ -47883,7 +49375,7 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B115" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(C110),2)</f>
@@ -47892,7 +49384,7 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B116" s="14" t="n">
         <f aca="false">ROUND(MIN(C111),2)</f>
@@ -47901,7 +49393,7 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B117" s="14" t="n">
         <f aca="false">ROUND(MAX(C112),2)</f>
@@ -47910,48 +49402,48 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C121" s="14" t="n">
         <f aca="false">B113</f>
         <v>5.99</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E121" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -47972,17 +49464,17 @@
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C122" s="14" t="n">
         <f aca="false">B114</f>
         <v>9.57</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E122" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48003,17 +49495,17 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C123" s="14" t="n">
         <f aca="false">B115</f>
         <v>16.2</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="E123" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -48034,12 +49526,12 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48047,29 +49539,29 @@
         <v>28</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B130" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48086,7 +49578,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B131" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -48103,7 +49595,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B132" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -48120,7 +49612,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B133" s="21" t="n">
         <f aca="false">Y!M29</f>
@@ -48137,7 +49629,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B134" s="21" t="n">
         <f aca="false">Y!N29</f>
@@ -48154,7 +49646,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B135" s="21" t="n">
         <f aca="false">Y!O29</f>
@@ -48171,27 +49663,27 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B137" s="19" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.201477501678979</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B138" s="21" t="n">
         <f aca="false">Y!D22/Y!D27*1000000</f>
@@ -48208,7 +49700,7 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B139" s="21" t="n">
         <f aca="false">Y!E22/Y!E27*1000000</f>
@@ -48225,7 +49717,7 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B140" s="21" t="n">
         <f aca="false">Y!F22/Y!F27*1000000</f>
@@ -48242,7 +49734,7 @@
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B141" s="21" t="n">
         <f aca="false">B133*(1-$B$137)</f>
@@ -48259,7 +49751,7 @@
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B142" s="21" t="n">
         <f aca="false">B134*(1-$B$137)</f>
@@ -48276,7 +49768,7 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B143" s="21" t="n">
         <f aca="false">B135*(1-$B$137)</f>
@@ -48293,7 +49785,7 @@
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B144" s="21" t="n">
         <f aca="false">SUMPRODUCT(B138:B143,1/(1+tp_r)^{1;2;3;4;5;6})+B143*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -48308,12 +49800,12 @@
         <v>1189912.86088635</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B145" s="21" t="n">
         <f aca="false">B144*(1+tp_r)</f>
@@ -48330,36 +49822,36 @@
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B146" s="25" t="n">
         <f aca="false">tp_wA*B145+tp_wB*C145+tp_wC*D145</f>
         <v>3709129.83314453</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>33</v>
@@ -48367,19 +49859,19 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C150" s="18" t="n">
         <v>1.26</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>59</v>
@@ -48387,19 +49879,19 @@
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C151" s="18" t="n">
         <v>3.35</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>59</v>
@@ -48407,19 +49899,19 @@
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="5" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C152" s="18" t="n">
         <v>2.22</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>59</v>
@@ -48427,19 +49919,19 @@
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C153" s="18" t="n">
         <v>1.66</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>59</v>
@@ -48447,55 +49939,55 @@
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B154" s="14" t="n">
         <f aca="false">MEDIAN(C150:C153)</f>
         <v>1.94</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B155" s="21" t="n">
         <f aca="false">tp_wA*Y!E28+tp_wB*Y!H28+tp_wC*Y!K28</f>
         <v>1271423.19481313</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B156" s="25" t="n">
         <f aca="false">B154*B155</f>
         <v>2466560.99793747</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B157" s="21" t="n">
         <f aca="false">tp_wA*(2/12*Y!D29+10/12*Y!E29)+tp_wB*(2/12*Y!G29+10/12*Y!H29)+tp_wC*(2/12*Y!J29+10/12*Y!K29)</f>
         <v>439185.328192061</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48503,29 +49995,29 @@
         <v>28</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C160" s="13"/>
       <c r="D160" s="13"/>
       <c r="E160" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B161" s="25" t="n">
         <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*B156</f>
         <v>3087845.415541</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B162" s="21" t="n">
         <f aca="false">B156</f>
@@ -48534,31 +50026,31 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B163" s="21" t="n">
         <f aca="false">cons_tp</f>
         <v>3096288</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="5" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B164" s="19" t="n">
         <f aca="false">B161/px-1</f>
         <v>1.41804652744009</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B165" s="19" t="n">
         <f aca="false">B162/px-1</f>
@@ -48567,7 +50059,7 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B166" s="26" t="n">
         <f aca="false">B145/px</f>
@@ -48582,36 +50074,36 @@
         <v>1.02498367030147</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B167" s="19" t="n">
         <f aca="false">B155/cons_bvps28-1</f>
         <v>-0.0906103007832535</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B168" s="19" t="n">
         <f aca="false">B157/(2/12*cons_eps27+10/12*cons_eps28)-1</f>
         <v>-0.167585820576288</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B169" s="19" t="n">
         <f aca="false">(cons_tp/cons_bvps28)/B154-1</f>
@@ -48624,19 +50116,19 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B170" s="27" t="str">
         <f aca="false">TEXT(D145,"#,##0")&amp;"～"&amp;TEXT(B145,"#,##0")</f>
         <v>1,308,904～6,513,978</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B171" s="15" t="n">
         <f aca="false">IF(px/Y!E28&gt;=MAX($B$68:$B$77),1,IF(px/Y!E28&lt;=MIN($B$68:$B$77),0,PERCENTRANK($B$68:$B$77,px/Y!E28)))</f>
@@ -48651,12 +50143,12 @@
         <v>0.185</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="B172" s="0" t="str">
         <f aca="false">"DCF：股東現金流 2027–2029 用每股（淨利＋折舊－資本支出），2030–2032 收斂期用 EPS ×（1 − g／ROE），r 10%、g 4%、ROE 為 2023–2025 平均（含 2023 虧損年）；明確期＋永續，基準日 2026 年底。Comparable：三星、美光、鎧俠、南亞科前瞻 P/B 中位數 × 2028 年底每股淨值（情境加權）。收斂期（2030–2032）淨利率"&amp;"收斂到循環中段：A 十年平均 × 1.2、B 十年平均、C 十年平均 × 0.8（In 頁 cyc_mA／cyc_mC），永續期以 2032 中段水準為基礎。偏誤：2027–2029 仍為高峰期盈餘且權重大，DCF 仍可能偏高估；同業 P/B 為循環高峰前的市場倍數、且 SK 海力士淨值增速高於同業，Comparable 方向不明。情境對應：A＝順利、B＝平平、C＝不如預期（原為 TrendFor"&amp;"ce／BofA 型價格情境）。"&amp;IF(MAX(B166:D166)&gt;3,"注意：DCF ÷ 現價有情境高於 3 倍（見上方「DCF ÷ 現價」列）；DCF 對收斂期淨利率與永續假設敏感，宜與 Comparable、市場共識並讀。","")</f>
@@ -48665,7 +50157,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48673,29 +50165,29 @@
         <v>28</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C175" s="13"/>
       <c r="D175" s="13"/>
       <c r="E175" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="5" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B176" s="21" t="n">
         <f aca="false">tp_wA*B178+tp_wB*B179+tp_wC*B180</f>
         <v>1392208.55280262</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B177" s="19" t="n">
         <f aca="false">B176/px-1</f>
@@ -48704,7 +50196,7 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="5" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B178" s="21" t="n">
         <f aca="false">B85*Y!D28</f>
@@ -48717,7 +50209,7 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B179" s="21" t="n">
         <f aca="false">B84*Y!G28</f>
@@ -48730,7 +50222,7 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B180" s="21" t="n">
         <f aca="false">B83*Y!J28</f>
@@ -48743,7 +50235,7 @@
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B181" s="15" t="n">
         <f aca="false">tp_wA</f>
@@ -48764,34 +50256,34 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="5" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="B184" s="27" t="str">
         <f aca="false">IF(B164&gt;0.5,"大於 50%",IF(B164&gt;0.25,"25%–50%",IF(B164&gt;=0,"0%–25%",IF(B164&gt;=-0.25,"0%～−25%",IF(B164&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>大於 50%</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B185" s="27" t="str">
         <f aca="false">IF(B164&gt;0.5,"強力買進",IF(B164&gt;0.25,"買進",IF(B164&gt;=-0.25,"中立",IF(B164&gt;=-0.5,"放空","強力放空"))))</f>
         <v>強力買進</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
   </sheetData>
@@ -48819,29 +50311,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>31</v>
@@ -48853,10 +50345,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -48873,10 +50365,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -48893,10 +50385,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -48913,10 +50405,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -48933,10 +50425,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -48953,10 +50445,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -48973,7 +50465,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>31</v>
@@ -48985,10 +50477,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -49005,10 +50497,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -49025,10 +50517,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -49045,10 +50537,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -49065,10 +50557,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -49085,10 +50577,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -49105,7 +50597,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>31</v>
@@ -49117,10 +50609,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -49137,10 +50629,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -49157,10 +50649,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -49177,10 +50669,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -49197,10 +50689,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -49217,10 +50709,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -49237,7 +50729,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>31</v>
@@ -49249,10 +50741,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -49269,10 +50761,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -49289,10 +50781,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -49309,10 +50801,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -49329,10 +50821,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -49349,10 +50841,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -49369,32 +50861,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49402,7 +50894,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49423,10 +50915,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C41" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r+0.01))^1+Val!B139/(1+(tp_r+0.01))^2+Val!B140/(1+(tp_r+0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C138/(1+(tp_r+0.01))^1+Val!C139/(1+(tp_r+0.01))^2+Val!C140/(1+(tp_r+0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D138/(1+(tp_r+0.01))^1+Val!D139/(1+(tp_r+0.01))^2+Val!D140/(1+(tp_r+0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -49447,10 +50939,10 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C42" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r-0.01))^1+Val!B139/(1+(tp_r-0.01))^2+Val!B140/(1+(tp_r-0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C138/(1+(tp_r-0.01))^1+Val!C139/(1+(tp_r-0.01))^2+Val!C140/(1+(tp_r-0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D138/(1+(tp_r-0.01))^1+Val!D139/(1+(tp_r-0.01))^2+Val!D140/(1+(tp_r-0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -49471,10 +50963,10 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C43" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49495,10 +50987,10 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C44" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49519,10 +51011,10 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C45" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49543,10 +51035,10 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C46" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49567,7 +51059,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="C47" s="28" t="n">
         <f aca="false">C40-Val!B146</f>
@@ -49599,7 +51091,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49607,21 +51099,21 @@
         <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Y!C4</f>
@@ -49635,12 +51127,12 @@
         <v>-0.00836946403295669</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!C14</f>
@@ -49654,12 +51146,12 @@
         <v>-0.000839616405542865</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!C20</f>
@@ -49673,12 +51165,12 @@
         <v>0.0337735275745357</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!C6</f>
@@ -49692,12 +51184,12 @@
         <v>-0.107661421776805</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!D4</f>
@@ -49711,12 +51203,12 @@
         <v>0.000398596474166402</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D14</f>
@@ -49730,12 +51222,12 @@
         <v>0.0515932496365124</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -49749,12 +51241,12 @@
         <v>0.0130416064099912</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!E14</f>
@@ -49768,12 +51260,12 @@
         <v>0.0571960438943868</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Q!H4</f>
@@ -49787,12 +51279,12 @@
         <v>0.0234999470244424</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">Q!H10</f>
@@ -49806,12 +51298,12 @@
         <v>-0.000178817722798708</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -49826,12 +51318,12 @@
         <v>0.156215042736661</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B15" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -49846,12 +51338,12 @@
         <v>0.328899445317256</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B16" s="17" t="n">
         <f aca="false">Y!E28</f>
@@ -49866,7 +51358,7 @@
         <v>0.0790737443350025</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx
+++ b/skhynix/dist/20261025_SK海力士模型_v0.5.1.xlsx
@@ -65,9 +65,17 @@
     <definedName function="false" hidden="false" name="cqA_14" vbProcedure="false">In!$E$94</definedName>
     <definedName function="false" hidden="false" name="cqA_15" vbProcedure="false">In!$E$95</definedName>
     <definedName function="false" hidden="false" name="cqA_16" vbProcedure="false">In!$E$96</definedName>
+    <definedName function="false" hidden="false" name="cqA_16_hi" vbProcedure="false">In!$F$96</definedName>
+    <definedName function="false" hidden="false" name="cqA_16_lo" vbProcedure="false">In!$D$96</definedName>
     <definedName function="false" hidden="false" name="cqA_17" vbProcedure="false">In!$E$97</definedName>
+    <definedName function="false" hidden="false" name="cqA_17_hi" vbProcedure="false">In!$F$97</definedName>
+    <definedName function="false" hidden="false" name="cqA_17_lo" vbProcedure="false">In!$D$97</definedName>
     <definedName function="false" hidden="false" name="cqA_18" vbProcedure="false">In!$E$98</definedName>
+    <definedName function="false" hidden="false" name="cqA_18_hi" vbProcedure="false">In!$F$98</definedName>
+    <definedName function="false" hidden="false" name="cqA_18_lo" vbProcedure="false">In!$D$98</definedName>
     <definedName function="false" hidden="false" name="cqA_19" vbProcedure="false">In!$E$99</definedName>
+    <definedName function="false" hidden="false" name="cqA_19_hi" vbProcedure="false">In!$F$99</definedName>
+    <definedName function="false" hidden="false" name="cqA_19_lo" vbProcedure="false">In!$D$99</definedName>
     <definedName function="false" hidden="false" name="cqA_8" vbProcedure="false">In!$E$88</definedName>
     <definedName function="false" hidden="false" name="cqA_9" vbProcedure="false">In!$E$89</definedName>
     <definedName function="false" hidden="false" name="cqB_10" vbProcedure="false">In!$E$102</definedName>
@@ -77,9 +85,17 @@
     <definedName function="false" hidden="false" name="cqB_14" vbProcedure="false">In!$E$106</definedName>
     <definedName function="false" hidden="false" name="cqB_15" vbProcedure="false">In!$E$107</definedName>
     <definedName function="false" hidden="false" name="cqB_16" vbProcedure="false">In!$E$108</definedName>
+    <definedName function="false" hidden="false" name="cqB_16_hi" vbProcedure="false">In!$F$108</definedName>
+    <definedName function="false" hidden="false" name="cqB_16_lo" vbProcedure="false">In!$D$108</definedName>
     <definedName function="false" hidden="false" name="cqB_17" vbProcedure="false">In!$E$109</definedName>
+    <definedName function="false" hidden="false" name="cqB_17_hi" vbProcedure="false">In!$F$109</definedName>
+    <definedName function="false" hidden="false" name="cqB_17_lo" vbProcedure="false">In!$D$109</definedName>
     <definedName function="false" hidden="false" name="cqB_18" vbProcedure="false">In!$E$110</definedName>
+    <definedName function="false" hidden="false" name="cqB_18_hi" vbProcedure="false">In!$F$110</definedName>
+    <definedName function="false" hidden="false" name="cqB_18_lo" vbProcedure="false">In!$D$110</definedName>
     <definedName function="false" hidden="false" name="cqB_19" vbProcedure="false">In!$E$111</definedName>
+    <definedName function="false" hidden="false" name="cqB_19_hi" vbProcedure="false">In!$F$111</definedName>
+    <definedName function="false" hidden="false" name="cqB_19_lo" vbProcedure="false">In!$D$111</definedName>
     <definedName function="false" hidden="false" name="cqB_8" vbProcedure="false">In!$E$100</definedName>
     <definedName function="false" hidden="false" name="cqB_9" vbProcedure="false">In!$E$101</definedName>
     <definedName function="false" hidden="false" name="cqC_10" vbProcedure="false">In!$E$114</definedName>
@@ -266,9 +282,17 @@
     <definedName function="false" hidden="false" name="nqA_14" vbProcedure="false">In!$E$137</definedName>
     <definedName function="false" hidden="false" name="nqA_15" vbProcedure="false">In!$E$138</definedName>
     <definedName function="false" hidden="false" name="nqA_16" vbProcedure="false">In!$E$139</definedName>
+    <definedName function="false" hidden="false" name="nqA_16_hi" vbProcedure="false">In!$F$139</definedName>
+    <definedName function="false" hidden="false" name="nqA_16_lo" vbProcedure="false">In!$D$139</definedName>
     <definedName function="false" hidden="false" name="nqA_17" vbProcedure="false">In!$E$140</definedName>
+    <definedName function="false" hidden="false" name="nqA_17_hi" vbProcedure="false">In!$F$140</definedName>
+    <definedName function="false" hidden="false" name="nqA_17_lo" vbProcedure="false">In!$D$140</definedName>
     <definedName function="false" hidden="false" name="nqA_18" vbProcedure="false">In!$E$141</definedName>
+    <definedName function="false" hidden="false" name="nqA_18_hi" vbProcedure="false">In!$F$141</definedName>
+    <definedName function="false" hidden="false" name="nqA_18_lo" vbProcedure="false">In!$D$141</definedName>
     <definedName function="false" hidden="false" name="nqA_19" vbProcedure="false">In!$E$142</definedName>
+    <definedName function="false" hidden="false" name="nqA_19_hi" vbProcedure="false">In!$F$142</definedName>
+    <definedName function="false" hidden="false" name="nqA_19_lo" vbProcedure="false">In!$D$142</definedName>
     <definedName function="false" hidden="false" name="nqA_8" vbProcedure="false">In!$E$131</definedName>
     <definedName function="false" hidden="false" name="nqA_9" vbProcedure="false">In!$E$132</definedName>
     <definedName function="false" hidden="false" name="nqB_10" vbProcedure="false">In!$E$145</definedName>
@@ -278,9 +302,17 @@
     <definedName function="false" hidden="false" name="nqB_14" vbProcedure="false">In!$E$149</definedName>
     <definedName function="false" hidden="false" name="nqB_15" vbProcedure="false">In!$E$150</definedName>
     <definedName function="false" hidden="false" name="nqB_16" vbProcedure="false">In!$E$151</definedName>
+    <definedName function="false" hidden="false" name="nqB_16_hi" vbProcedure="false">In!$F$151</definedName>
+    <definedName function="false" hidden="false" name="nqB_16_lo" vbProcedure="false">In!$D$151</definedName>
     <definedName function="false" hidden="false" name="nqB_17" vbProcedure="false">In!$E$152</definedName>
+    <definedName function="false" hidden="false" name="nqB_17_hi" vbProcedure="false">In!$F$152</definedName>
+    <definedName function="false" hidden="false" name="nqB_17_lo" vbProcedure="false">In!$D$152</definedName>
     <definedName function="false" hidden="false" name="nqB_18" vbProcedure="false">In!$E$153</definedName>
+    <definedName function="false" hidden="false" name="nqB_18_hi" vbProcedure="false">In!$F$153</definedName>
+    <definedName function="false" hidden="false" name="nqB_18_lo" vbProcedure="false">In!$D$153</definedName>
     <definedName function="false" hidden="false" name="nqB_19" vbProcedure="false">In!$E$154</definedName>
+    <definedName function="false" hidden="false" name="nqB_19_hi" vbProcedure="false">In!$F$154</definedName>
+    <definedName function="false" hidden="false" name="nqB_19_lo" vbProcedure="false">In!$D$154</definedName>
     <definedName function="false" hidden="false" name="nqB_8" vbProcedure="false">In!$E$143</definedName>
     <definedName function="false" hidden="false" name="nqB_9" vbProcedure="false">In!$E$144</definedName>
     <definedName function="false" hidden="false" name="nqC_10" vbProcedure="false">In!$E$157</definedName>
@@ -482,7 +514,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2063" uniqueCount="1081">
   <si>
     <r>
       <rPr>
@@ -5903,39 +5935,67 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Micron</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：產業 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中 </t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美光 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FQ4-26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法說：產業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">皆中 </t>
     </r>
     <r>
       <rPr>
@@ -5954,7 +6014,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">段</t>
+      <t xml:space="preserve">段；本模型取低於產業（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士優先高價值產品，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 NAND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位元季減）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：原標 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Verified </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不當</t>
     </r>
   </si>
   <si>
@@ -8642,6 +8778,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -8769,7 +8914,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">緩降</t>
+      <t xml:space="preserve">緩降（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -9341,6 +9505,103 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為本庫外推：標示來源只涵蓋到 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核）；區間＝情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同季值</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">cqA_17</t>
   </si>
   <si>
@@ -9629,6 +9890,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -9756,7 +10026,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">溫和回升</t>
+      <t xml:space="preserve">溫和回升（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -12110,6 +12399,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -12142,7 +12440,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">下半年供需平衡、價格面臨下修壓力</t>
+      <t xml:space="preserve">下半年供需平衡、價格面臨下修壓力（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -12894,6 +13211,15 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本庫情境路徑，依據：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
@@ -12956,6 +13282,34 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">NAND $/GB 2028 −68.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核：來源無逐季數字，逐季值為本庫拆分）</t>
     </r>
   </si>
   <si>
@@ -37249,63 +37603,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
         <v>4.46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
         <v>216 ／ 260</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
         <v>55 ／ 154</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
         <v>1.23255275</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>166</v>
@@ -37336,31 +37690,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37368,87 +37722,87 @@
         <v>214</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>1079</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>1078</v>
       </c>
     </row>
   </sheetData>
@@ -37955,9 +38309,9 @@
         <v>0.25</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -37981,7 +38335,7 @@
         <v>0.25</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>99</v>
@@ -39250,9 +39604,9 @@
         <v>0.03</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H88" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H88" s="5" t="s">
         <v>259</v>
       </c>
     </row>
@@ -39270,7 +39624,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>99</v>
@@ -39290,7 +39644,7 @@
         <v>-0.02</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H90" s="5" t="s">
         <v>99</v>
@@ -39310,7 +39664,7 @@
         <v>-0.03</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>99</v>
@@ -39330,7 +39684,7 @@
         <v>-0.03</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>99</v>
@@ -39350,7 +39704,7 @@
         <v>-0.03</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>99</v>
@@ -39370,7 +39724,7 @@
         <v>-0.02</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>99</v>
@@ -39390,7 +39744,7 @@
         <v>-0.02</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>99</v>
@@ -39406,31 +39760,43 @@
       <c r="C96" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D96" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E96" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F96" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G96" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>99</v>
+        <v>63</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C97" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D97" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E97" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F97" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G97" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>99</v>
@@ -39438,19 +39804,25 @@
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D98" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E98" s="7" t="n">
         <v>-0.02</v>
       </c>
+      <c r="F98" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G98" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>99</v>
@@ -39458,19 +39830,25 @@
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D99" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E99" s="7" t="n">
         <v>-0.02</v>
       </c>
+      <c r="F99" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G99" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>99</v>
@@ -39478,10 +39856,10 @@
     </row>
     <row r="100" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>49</v>
@@ -39490,18 +39868,18 @@
         <v>0.05</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>284</v>
+        <v>39</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>49</v>
@@ -39510,7 +39888,7 @@
         <v>0.02</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>99</v>
@@ -39518,10 +39896,10 @@
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C102" s="0" t="s">
         <v>49</v>
@@ -39530,7 +39908,7 @@
         <v>-0.08</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>99</v>
@@ -39538,10 +39916,10 @@
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C103" s="0" t="s">
         <v>49</v>
@@ -39550,7 +39928,7 @@
         <v>-0.15</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>99</v>
@@ -39558,10 +39936,10 @@
     </row>
     <row r="104" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>49</v>
@@ -39570,7 +39948,7 @@
         <v>-0.25</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>99</v>
@@ -39578,10 +39956,10 @@
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>49</v>
@@ -39590,7 +39968,7 @@
         <v>-0.15</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>99</v>
@@ -39598,10 +39976,10 @@
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>49</v>
@@ -39610,7 +39988,7 @@
         <v>-0.1</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H106" s="5" t="s">
         <v>99</v>
@@ -39618,10 +39996,10 @@
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C107" s="0" t="s">
         <v>49</v>
@@ -39630,7 +40008,7 @@
         <v>-0.05</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H107" s="5" t="s">
         <v>99</v>
@@ -39638,39 +40016,51 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D108" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E108" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F108" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G108" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H108" s="5" t="s">
-        <v>99</v>
+        <v>63</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D109" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E109" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F109" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G109" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>99</v>
@@ -39678,19 +40068,25 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C110" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D110" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E110" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F110" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G110" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>99</v>
@@ -39698,19 +40094,25 @@
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C111" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D111" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E111" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F111" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G111" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>99</v>
@@ -39718,10 +40120,10 @@
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>49</v>
@@ -39739,15 +40141,15 @@
         <v>63</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C113" s="0" t="s">
         <v>49</v>
@@ -39770,10 +40172,10 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C114" s="0" t="s">
         <v>49</v>
@@ -39796,10 +40198,10 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C115" s="0" t="s">
         <v>49</v>
@@ -39822,10 +40224,10 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C116" s="0" t="s">
         <v>49</v>
@@ -39848,10 +40250,10 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C117" s="0" t="s">
         <v>49</v>
@@ -39874,10 +40276,10 @@
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C118" s="0" t="s">
         <v>49</v>
@@ -39900,10 +40302,10 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C119" s="0" t="s">
         <v>49</v>
@@ -39926,10 +40328,10 @@
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>49</v>
@@ -39952,10 +40354,10 @@
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C121" s="0" t="s">
         <v>49</v>
@@ -39978,10 +40380,10 @@
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C122" s="0" t="s">
         <v>49</v>
@@ -40004,10 +40406,10 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C123" s="0" t="s">
         <v>49</v>
@@ -40030,10 +40432,10 @@
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B124" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C124" s="0" t="s">
         <v>49</v>
@@ -40045,15 +40447,15 @@
         <v>59</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>49</v>
@@ -40070,10 +40472,10 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C126" s="0" t="s">
         <v>49</v>
@@ -40090,10 +40492,10 @@
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C127" s="0" t="s">
         <v>49</v>
@@ -40110,10 +40512,10 @@
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B128" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C128" s="0" t="s">
         <v>49</v>
@@ -40130,10 +40532,10 @@
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C129" s="0" t="s">
         <v>49</v>
@@ -40150,10 +40552,10 @@
     </row>
     <row r="130" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B130" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C130" s="0" t="s">
         <v>49</v>
@@ -40170,10 +40572,10 @@
     </row>
     <row r="131" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B131" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C131" s="0" t="s">
         <v>49</v>
@@ -40182,18 +40584,18 @@
         <v>0.03</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H131" s="8" t="s">
-        <v>349</v>
+        <v>39</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B132" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C132" s="0" t="s">
         <v>49</v>
@@ -40202,7 +40604,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H132" s="5" t="s">
         <v>99</v>
@@ -40210,10 +40612,10 @@
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B133" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C133" s="0" t="s">
         <v>49</v>
@@ -40222,7 +40624,7 @@
         <v>-0.05</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H133" s="5" t="s">
         <v>99</v>
@@ -40230,10 +40632,10 @@
     </row>
     <row r="134" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C134" s="0" t="s">
         <v>49</v>
@@ -40242,7 +40644,7 @@
         <v>-0.07</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H134" s="5" t="s">
         <v>99</v>
@@ -40250,10 +40652,10 @@
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C135" s="0" t="s">
         <v>49</v>
@@ -40262,7 +40664,7 @@
         <v>-0.05</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H135" s="5" t="s">
         <v>99</v>
@@ -40270,10 +40672,10 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C136" s="0" t="s">
         <v>49</v>
@@ -40282,7 +40684,7 @@
         <v>-0.05</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H136" s="5" t="s">
         <v>99</v>
@@ -40290,10 +40692,10 @@
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C137" s="0" t="s">
         <v>49</v>
@@ -40302,7 +40704,7 @@
         <v>-0.05</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>99</v>
@@ -40310,10 +40712,10 @@
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C138" s="0" t="s">
         <v>49</v>
@@ -40322,7 +40724,7 @@
         <v>-0.05</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H138" s="5" t="s">
         <v>99</v>
@@ -40330,39 +40732,51 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C139" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D139" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E139" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F139" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G139" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H139" s="5" t="s">
-        <v>99</v>
+        <v>63</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B140" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C140" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D140" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E140" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F140" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G140" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H140" s="5" t="s">
         <v>99</v>
@@ -40370,19 +40784,25 @@
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C141" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D141" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E141" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F141" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G141" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H141" s="5" t="s">
         <v>99</v>
@@ -40390,19 +40810,25 @@
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B142" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D142" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E142" s="7" t="n">
         <v>-0.03</v>
       </c>
+      <c r="F142" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G142" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H142" s="5" t="s">
         <v>99</v>
@@ -40410,10 +40836,10 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B143" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C143" s="0" t="s">
         <v>49</v>
@@ -40422,18 +40848,18 @@
         <v>0.05</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H143" s="8" t="s">
-        <v>374</v>
+        <v>39</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B144" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C144" s="0" t="s">
         <v>49</v>
@@ -40442,7 +40868,7 @@
         <v>0.02</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H144" s="5" t="s">
         <v>99</v>
@@ -40450,10 +40876,10 @@
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B145" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>49</v>
@@ -40462,7 +40888,7 @@
         <v>-0.1</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H145" s="5" t="s">
         <v>99</v>
@@ -40470,10 +40896,10 @@
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B146" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C146" s="0" t="s">
         <v>49</v>
@@ -40482,7 +40908,7 @@
         <v>-0.2</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H146" s="5" t="s">
         <v>99</v>
@@ -40490,10 +40916,10 @@
     </row>
     <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B147" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C147" s="0" t="s">
         <v>49</v>
@@ -40502,7 +40928,7 @@
         <v>-0.3</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H147" s="5" t="s">
         <v>99</v>
@@ -40510,10 +40936,10 @@
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B148" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C148" s="0" t="s">
         <v>49</v>
@@ -40522,7 +40948,7 @@
         <v>-0.25</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H148" s="5" t="s">
         <v>99</v>
@@ -40530,10 +40956,10 @@
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B149" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C149" s="0" t="s">
         <v>49</v>
@@ -40542,7 +40968,7 @@
         <v>-0.2</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H149" s="5" t="s">
         <v>99</v>
@@ -40550,10 +40976,10 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C150" s="0" t="s">
         <v>49</v>
@@ -40562,7 +40988,7 @@
         <v>-0.1</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="H150" s="5" t="s">
         <v>99</v>
@@ -40570,39 +40996,51 @@
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C151" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D151" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E151" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F151" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G151" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H151" s="5" t="s">
-        <v>99</v>
+        <v>63</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C152" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D152" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E152" s="7" t="n">
         <v>0.05</v>
       </c>
+      <c r="F152" s="7" t="n">
+        <v>0.05</v>
+      </c>
       <c r="G152" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H152" s="5" t="s">
         <v>99</v>
@@ -40610,19 +41048,25 @@
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C153" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D153" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E153" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F153" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G153" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H153" s="5" t="s">
         <v>99</v>
@@ -40630,19 +41074,25 @@
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B154" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C154" s="0" t="s">
         <v>49</v>
       </c>
+      <c r="D154" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E154" s="7" t="n">
         <v>0.03</v>
       </c>
+      <c r="F154" s="7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G154" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H154" s="5" t="s">
         <v>99</v>
@@ -40650,10 +41100,10 @@
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B155" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C155" s="0" t="s">
         <v>49</v>
@@ -40671,15 +41121,15 @@
         <v>63</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B156" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C156" s="0" t="s">
         <v>49</v>
@@ -40702,10 +41152,10 @@
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B157" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C157" s="0" t="s">
         <v>49</v>
@@ -40728,10 +41178,10 @@
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B158" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C158" s="0" t="s">
         <v>49</v>
@@ -40754,10 +41204,10 @@
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B159" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C159" s="0" t="s">
         <v>49</v>
@@ -40780,10 +41230,10 @@
     </row>
     <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B160" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C160" s="0" t="s">
         <v>49</v>
@@ -40806,10 +41256,10 @@
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B161" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C161" s="0" t="s">
         <v>49</v>
@@ -40832,10 +41282,10 @@
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B162" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C162" s="0" t="s">
         <v>49</v>
@@ -40858,10 +41308,10 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B163" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C163" s="0" t="s">
         <v>49</v>
@@ -40884,10 +41334,10 @@
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C164" s="0" t="s">
         <v>49</v>
@@ -40910,10 +41360,10 @@
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>49</v>
@@ -40936,10 +41386,10 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B166" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C166" s="0" t="s">
         <v>49</v>
@@ -40962,18 +41412,18 @@
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B168" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E168" s="7" t="n">
         <v>5.4</v>
@@ -40982,18 +41432,18 @@
         <v>59</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B169" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E169" s="7" t="n">
         <v>2.4</v>
@@ -41007,13 +41457,13 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B170" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E170" s="7" t="n">
         <v>0.5</v>
@@ -41027,13 +41477,13 @@
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B171" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E171" s="7" t="n">
         <v>260</v>
@@ -41047,13 +41497,13 @@
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="B172" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="C172" s="0" t="s">
         <v>434</v>
-      </c>
-      <c r="B172" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="C172" s="0" t="s">
-        <v>433</v>
       </c>
       <c r="E172" s="7" t="n">
         <v>280</v>
@@ -41067,13 +41517,13 @@
     </row>
     <row r="173" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B173" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E173" s="7" t="n">
         <v>288</v>
@@ -41087,13 +41537,13 @@
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E174" s="7" t="n">
         <v>1.7</v>
@@ -41102,18 +41552,18 @@
         <v>59</v>
       </c>
       <c r="H174" s="8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B175" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E175" s="7" t="n">
         <v>7</v>
@@ -41127,13 +41577,13 @@
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B176" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E176" s="7" t="n">
         <v>7</v>
@@ -41147,13 +41597,13 @@
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B177" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E177" s="7" t="n">
         <v>288</v>
@@ -41167,13 +41617,13 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B178" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E178" s="7" t="n">
         <v>288</v>
@@ -41187,13 +41637,13 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B179" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E179" s="7" t="n">
         <v>288</v>
@@ -41207,13 +41657,13 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B180" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D180" s="7" t="n">
         <v>0</v>
@@ -41228,18 +41678,18 @@
         <v>63</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D181" s="7" t="n">
         <v>0</v>
@@ -41259,13 +41709,13 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B182" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D182" s="7" t="n">
         <v>1</v>
@@ -41285,13 +41735,13 @@
     </row>
     <row r="183" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B183" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E183" s="7" t="n">
         <v>1024</v>
@@ -41300,18 +41750,18 @@
         <v>59</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E184" s="7" t="n">
         <v>1024</v>
@@ -41325,13 +41775,13 @@
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E185" s="7" t="n">
         <v>1024</v>
@@ -41345,13 +41795,13 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E186" s="7" t="n">
         <v>0.5</v>
@@ -41360,18 +41810,18 @@
         <v>59</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E187" s="7" t="n">
         <v>0</v>
@@ -41385,13 +41835,13 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E188" s="7" t="n">
         <v>0</v>
@@ -41405,13 +41855,13 @@
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E189" s="7" t="n">
         <v>141</v>
@@ -41425,13 +41875,13 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E190" s="7" t="n">
         <v>141</v>
@@ -41445,13 +41895,13 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E191" s="7" t="n">
         <v>141</v>
@@ -41465,13 +41915,13 @@
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D192" s="7" t="n">
         <v>0.6</v>
@@ -41483,21 +41933,21 @@
         <v>0.9</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D193" s="7" t="n">
         <v>1.2</v>
@@ -41509,7 +41959,7 @@
         <v>1.8</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H193" s="5" t="s">
         <v>99</v>
@@ -41517,13 +41967,13 @@
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D194" s="7" t="n">
         <v>1.5</v>
@@ -41535,7 +41985,7 @@
         <v>2.5</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H194" s="5" t="s">
         <v>99</v>
@@ -41543,13 +41993,13 @@
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D195" s="7" t="n">
         <v>288</v>
@@ -41561,7 +42011,7 @@
         <v>288</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H195" s="5" t="s">
         <v>99</v>
@@ -41569,13 +42019,13 @@
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D196" s="7" t="n">
         <v>288</v>
@@ -41587,7 +42037,7 @@
         <v>432</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H196" s="5" t="s">
         <v>99</v>
@@ -41595,13 +42045,13 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D197" s="7" t="n">
         <v>432</v>
@@ -41613,7 +42063,7 @@
         <v>432</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H197" s="5" t="s">
         <v>99</v>
@@ -41621,13 +42071,13 @@
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E198" s="7" t="n">
         <v>3.85</v>
@@ -41636,18 +42086,18 @@
         <v>59</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E199" s="7" t="n">
         <v>5.5</v>
@@ -41661,13 +42111,13 @@
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E200" s="7" t="n">
         <v>7</v>
@@ -41681,13 +42131,13 @@
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E201" s="7" t="n">
         <v>192</v>
@@ -41701,13 +42151,13 @@
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E202" s="7" t="n">
         <v>250</v>
@@ -41721,13 +42171,13 @@
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E203" s="7" t="n">
         <v>288</v>
@@ -41741,13 +42191,13 @@
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D204" s="7" t="n">
         <v>1.5</v>
@@ -41762,18 +42212,18 @@
         <v>63</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D205" s="7" t="n">
         <v>2</v>
@@ -41793,13 +42243,13 @@
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D206" s="7" t="n">
         <v>2</v>
@@ -41819,13 +42269,13 @@
     </row>
     <row r="207" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D207" s="7" t="n">
         <v>96</v>
@@ -41845,13 +42295,13 @@
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D208" s="7" t="n">
         <v>120</v>
@@ -41871,13 +42321,13 @@
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D209" s="7" t="n">
         <v>144</v>
@@ -41897,13 +42347,13 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D210" s="7" t="n">
         <v>0.5</v>
@@ -41915,21 +42365,21 @@
         <v>1.5</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D211" s="7" t="n">
         <v>3</v>
@@ -41941,7 +42391,7 @@
         <v>6</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H211" s="5" t="s">
         <v>99</v>
@@ -41949,13 +42399,13 @@
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D212" s="7" t="n">
         <v>3.5</v>
@@ -41967,7 +42417,7 @@
         <v>7</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H212" s="5" t="s">
         <v>99</v>
@@ -41975,13 +42425,13 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D213" s="7" t="n">
         <v>100</v>
@@ -41993,7 +42443,7 @@
         <v>200</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H213" s="5" t="s">
         <v>99</v>
@@ -42001,13 +42451,13 @@
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D214" s="7" t="n">
         <v>150</v>
@@ -42019,7 +42469,7 @@
         <v>250</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H214" s="5" t="s">
         <v>99</v>
@@ -42027,13 +42477,13 @@
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D215" s="7" t="n">
         <v>200</v>
@@ -42045,7 +42495,7 @@
         <v>300</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H215" s="5" t="s">
         <v>99</v>
@@ -42053,15 +42503,15 @@
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>226</v>
@@ -42073,15 +42523,15 @@
         <v>39</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C218" s="0" t="s">
         <v>226</v>
@@ -42098,10 +42548,10 @@
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C219" s="0" t="s">
         <v>226</v>
@@ -42124,10 +42574,10 @@
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>226</v>
@@ -42150,10 +42600,10 @@
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>226</v>
@@ -42176,10 +42626,10 @@
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>226</v>
@@ -42202,18 +42652,18 @@
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D224" s="7" t="n">
         <v>34</v>
@@ -42228,15 +42678,15 @@
         <v>44</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>49</v>
@@ -42254,15 +42704,15 @@
         <v>59</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>226</v>
@@ -42280,15 +42730,15 @@
         <v>63</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>49</v>
@@ -42306,15 +42756,15 @@
         <v>59</v>
       </c>
       <c r="H227" s="8" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>49</v>
@@ -42332,18 +42782,18 @@
         <v>63</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D229" s="7" t="n">
         <v>12.5</v>
@@ -42358,15 +42808,15 @@
         <v>59</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>49</v>
@@ -42384,15 +42834,15 @@
         <v>59</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C231" s="0" t="s">
         <v>49</v>
@@ -42410,15 +42860,15 @@
         <v>59</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>49</v>
@@ -42436,15 +42886,15 @@
         <v>63</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>49</v>
@@ -42462,15 +42912,15 @@
         <v>63</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>49</v>
@@ -42488,15 +42938,15 @@
         <v>63</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C235" s="0" t="s">
         <v>49</v>
@@ -42514,15 +42964,15 @@
         <v>63</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>49</v>
@@ -42540,15 +42990,15 @@
         <v>63</v>
       </c>
       <c r="H236" s="8" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C237" s="0" t="s">
         <v>49</v>
@@ -42566,15 +43016,15 @@
         <v>63</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C238" s="0" t="s">
         <v>49</v>
@@ -42592,23 +43042,23 @@
         <v>63</v>
       </c>
       <c r="H238" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D240" s="7" t="n">
         <v>340</v>
@@ -42620,21 +43070,21 @@
         <v>400</v>
       </c>
       <c r="G240" s="8" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D241" s="7" t="n">
         <v>38</v>
@@ -42649,18 +43099,18 @@
         <v>39</v>
       </c>
       <c r="H241" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D242" s="7" t="n">
         <v>3.5</v>
@@ -42675,18 +43125,18 @@
         <v>39</v>
       </c>
       <c r="H242" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E243" s="7" t="n">
         <v>54.6</v>
@@ -42695,18 +43145,18 @@
         <v>59</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E244" s="7" t="n">
         <v>77.4</v>
@@ -42715,18 +43165,18 @@
         <v>59</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E245" s="7" t="n">
         <v>152.8</v>
@@ -42735,20 +43185,20 @@
         <v>59</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C247" s="9" t="s">
         <v>49</v>
@@ -42762,15 +43212,15 @@
         <v>63</v>
       </c>
       <c r="H247" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C248" s="9" t="s">
         <v>49</v>
@@ -42784,15 +43234,15 @@
         <v>63</v>
       </c>
       <c r="H248" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C249" s="9" t="s">
         <v>49</v>
@@ -42806,15 +43256,15 @@
         <v>63</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C250" s="9" t="s">
         <v>49</v>
@@ -42828,15 +43278,15 @@
         <v>63</v>
       </c>
       <c r="H250" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C251" s="9" t="s">
         <v>49</v>
@@ -42850,15 +43300,15 @@
         <v>63</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>49</v>
@@ -42873,15 +43323,15 @@
         <v>39</v>
       </c>
       <c r="H252" s="9" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C253" s="9" t="s">
         <v>49</v>
@@ -42895,15 +43345,15 @@
         <v>63</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C254" s="9" t="s">
         <v>49</v>
@@ -42918,15 +43368,15 @@
         <v>39</v>
       </c>
       <c r="H254" s="9" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C255" s="9" t="s">
         <v>49</v>
@@ -42941,15 +43391,15 @@
         <v>63</v>
       </c>
       <c r="H255" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C256" s="9" t="s">
         <v>49</v>
@@ -42964,15 +43414,15 @@
         <v>63</v>
       </c>
       <c r="H256" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C257" s="9" t="s">
         <v>49</v>
@@ -42987,15 +43437,15 @@
         <v>63</v>
       </c>
       <c r="H257" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="9" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C258" s="9" t="s">
         <v>226</v>
@@ -43009,15 +43459,15 @@
         <v>63</v>
       </c>
       <c r="H258" s="9" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="9" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C259" s="9" t="s">
         <v>226</v>
@@ -43031,15 +43481,15 @@
         <v>63</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C260" s="9" t="s">
         <v>49</v>
@@ -43054,15 +43504,15 @@
         <v>39</v>
       </c>
       <c r="H260" s="9" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C261" s="9" t="s">
         <v>49</v>
@@ -43077,15 +43527,15 @@
         <v>39</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="9" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C262" s="9" t="s">
         <v>49</v>
@@ -43100,15 +43550,15 @@
         <v>39</v>
       </c>
       <c r="H262" s="9" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="9" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C263" s="9" t="s">
         <v>43</v>
@@ -43126,15 +43576,15 @@
         <v>59</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="9" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C264" s="9" t="s">
         <v>43</v>
@@ -43148,15 +43598,15 @@
         <v>59</v>
       </c>
       <c r="H264" s="9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="9" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C265" s="9" t="s">
         <v>43</v>
@@ -43170,15 +43620,15 @@
         <v>59</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="9" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C266" s="9" t="s">
         <v>43</v>
@@ -43192,7 +43642,7 @@
         <v>59</v>
       </c>
       <c r="H266" s="9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>
@@ -43220,83 +43670,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="V3" s="13" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
@@ -43380,10 +43830,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
@@ -43467,10 +43917,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
@@ -43554,10 +44004,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
@@ -43641,10 +44091,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
@@ -43728,10 +44178,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
+        <v>696</v>
+      </c>
+      <c r="B10" s="0" t="s">
         <v>695</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>694</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
@@ -43815,50 +44265,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">AVERAGE(C4:F4)</f>
@@ -43899,10 +44349,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">AVERAGE(C5:F5)</f>
@@ -43943,10 +44393,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">AVERAGE(C6:F6)</f>
@@ -43987,10 +44437,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">AVERAGE(C8:F8)</f>
@@ -44031,10 +44481,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">AVERAGE(C9:F9)</f>
@@ -44075,10 +44525,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
+        <v>696</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>695</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>694</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">AVERAGE(C10:F10)</f>
@@ -44143,7 +44593,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44154,35 +44604,35 @@
         <v>29</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">u_bw_26*g_bw_26</f>
@@ -44199,10 +44649,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>712</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>711</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>710</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">u_rb_26*g_rb_26</f>
@@ -44219,10 +44669,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">u_ru_26*g_ru_26</f>
@@ -44239,10 +44689,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">u_hp_26*g_hp_26</f>
@@ -44259,10 +44709,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">u_amd_26*g_amd_26</f>
@@ -44279,10 +44729,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">u_tpu_26*g_tpu_26</f>
@@ -44299,10 +44749,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">u_trn_26*g_trn_26</f>
@@ -44319,10 +44769,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">u_oth_26*g_oth_26</f>
@@ -44339,10 +44789,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">SUM(D5:D12)/1000</f>
@@ -44363,10 +44813,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>720</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>719</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D13*hbm_gross</f>
@@ -44387,10 +44837,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">u_bw_26+u_rb_26+u_ru_26+u_hp_26+u_amd_26+u_tpu_26+u_trn_26+u_oth_26</f>
@@ -44405,15 +44855,15 @@
         <v>26.5</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D16" s="16" t="n">
         <f aca="false">D13*1000/D15</f>
@@ -44430,10 +44880,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">D17/(1+hbm_g26)</f>
@@ -44456,12 +44906,12 @@
         <v>11.477169466875</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>226</v>
@@ -44481,12 +44931,12 @@
         <v>1</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>226</v>
@@ -44506,12 +44956,12 @@
         <v>0.85</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>226</v>
@@ -44531,15 +44981,15 @@
         <v>0.6</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">D14*D18</f>
@@ -44560,10 +45010,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">D14*D19</f>
@@ -44584,10 +45034,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">D14*D20</f>
@@ -44608,10 +45058,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">C17</f>
@@ -44634,15 +45084,15 @@
         <v>11.477169466875</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">C17</f>
@@ -44667,10 +45117,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">C17</f>
@@ -44695,10 +45145,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D27" s="14" t="n">
         <f aca="false">D21-D17</f>
@@ -44719,10 +45169,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">D22-D17</f>
@@ -44743,10 +45193,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">D23-D17</f>
@@ -44767,10 +45217,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C30" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -44795,10 +45245,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -44823,10 +45273,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -44851,10 +45301,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">C24*C30</f>
@@ -44879,10 +45329,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">C25*C31</f>
@@ -44907,10 +45357,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">C26*C32</f>
@@ -44935,15 +45385,15 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">(D5+D6+D7+D8)/1000*hbm_p26</f>
@@ -44952,22 +45402,22 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">nv_dc26*nv_hbm/nv_content</f>
         <v>38.9728971962617</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>49</v>
@@ -44979,10 +45429,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D41" s="17" t="n">
         <f aca="false">nv_dc26/nv_content</f>
@@ -44993,15 +45443,15 @@
         <v>7.6</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">pub26_lo</f>
@@ -45018,7 +45468,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>49</v>
@@ -45057,7 +45507,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45065,36 +45515,36 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>17.639</v>
@@ -45129,7 +45579,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">F4*0.773</f>
@@ -45154,7 +45604,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F6" s="14" t="n">
         <f aca="false">F4*0.22</f>
@@ -45179,7 +45629,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">F4-F5-F6</f>
@@ -45204,7 +45654,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">F4*(1-0.79)</f>
@@ -45229,7 +45679,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">F4-F8-F10</f>
@@ -45254,7 +45704,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>7.441</v>
@@ -45289,7 +45739,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IF(B4=0,"",B10/B4)</f>
@@ -45330,7 +45780,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>8.108</v>
@@ -45365,7 +45815,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>3.334</v>
@@ -45400,7 +45850,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G14" s="0" t="n">
         <v>1</v>
@@ -45416,7 +45866,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>1</v>
@@ -45432,7 +45882,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
@@ -45461,12 +45911,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45474,72 +45924,72 @@
         <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">SUM(Q!B4:E4)</f>
@@ -45588,7 +46038,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">Q!J5-C6</f>
@@ -45631,12 +46081,12 @@
         <v>99.342377931568</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">(Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26)*fx/1000</f>
@@ -45679,12 +46129,12 @@
         <v>75.3957801559872</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">Q!J6</f>
@@ -45729,7 +46179,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">Q!J7</f>
@@ -45774,7 +46224,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">C6/C4</f>
@@ -45819,7 +46269,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUM(Q!B13:E13)</f>
@@ -45868,7 +46318,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">w_c*(1+cb_1)+w_h*D31/C31+w_n*(1+nb_1)</f>
@@ -45909,7 +46359,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">Q!J8</f>
@@ -45952,12 +46402,12 @@
         <v>79.3034449351957</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">Q!J9</f>
@@ -46002,7 +46452,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">SUM(Q!B10:E10)</f>
@@ -46051,7 +46501,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B14/B4</f>
@@ -46100,7 +46550,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">nm_rev_0</f>
@@ -46145,7 +46595,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">nm_op_0</f>
@@ -46190,7 +46640,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C4+C16</f>
@@ -46269,12 +46719,12 @@
         <v>216.483583576036</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C14+C17</f>
@@ -46319,7 +46769,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">SUM(Q!B12:E12)</f>
@@ -46402,12 +46852,12 @@
         <v>32.3783962634274</v>
       </c>
       <c r="V20" s="5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">cap_0</f>
@@ -46452,7 +46902,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">C20+C10-C21</f>
@@ -46497,7 +46947,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">div_0</f>
@@ -46542,7 +46992,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">bb_0</f>
@@ -46585,12 +47035,12 @@
         <v>28.3807982239078</v>
       </c>
       <c r="V24" s="5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">eq_last+(Q!H12+Q!I12)+extra_eq-C24-C23</f>
@@ -46635,7 +47085,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">nc_last+(Q!H12+Q!I12)+(Q!H13+Q!I13)-capex_rem+extra_eq-C24-C23</f>
@@ -46680,7 +47130,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">sh_last+extra_sh-bb_sh_0</f>
@@ -46761,7 +47211,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">C25/C27*1000000</f>
@@ -46806,7 +47256,7 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">C20/C27*1000000</f>
@@ -46887,7 +47337,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">C20/C25</f>
@@ -46932,7 +47382,7 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">(Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26)</f>
@@ -46977,7 +47427,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">D18/C18-1</f>
@@ -47054,7 +47504,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">C20/C18</f>
@@ -47163,30 +47613,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47198,10 +47648,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E4" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -47218,17 +47668,17 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E5" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -47245,17 +47695,17 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -47279,10 +47729,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47299,17 +47749,17 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E8" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47326,17 +47776,17 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47360,10 +47810,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -47380,17 +47830,17 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -47407,17 +47857,17 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -47441,10 +47891,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E13" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -47461,17 +47911,17 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E14" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -47488,17 +47938,17 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E15" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -47522,10 +47972,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E16" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -47542,17 +47992,17 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E17" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -47569,17 +48019,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E18" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -47603,10 +48053,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E19" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -47623,17 +48073,17 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E20" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -47650,17 +48100,17 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E21" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -47684,10 +48134,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E22" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -47704,17 +48154,17 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E23" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -47731,17 +48181,17 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E24" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -47765,10 +48215,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E25" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -47785,17 +48235,17 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E26" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -47812,17 +48262,17 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E27" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -47846,10 +48296,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E28" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -47866,17 +48316,17 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B29" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -47893,17 +48343,17 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E30" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -47927,10 +48377,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E31" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -47947,17 +48397,17 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.6</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E32" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -47974,17 +48424,17 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>3.3</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E33" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -48008,10 +48458,10 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E34" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48035,10 +48485,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E35" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48062,10 +48512,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E36" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48089,10 +48539,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E37" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -48116,10 +48566,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E38" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -48143,10 +48593,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E39" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -48170,10 +48620,10 @@
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E40" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -48197,10 +48647,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E41" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -48224,10 +48674,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E42" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -48251,10 +48701,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E43" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -48278,10 +48728,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E44" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -48305,10 +48755,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E45" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -48332,10 +48782,10 @@
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E46" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -48359,10 +48809,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E47" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -48386,10 +48836,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E48" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -48413,10 +48863,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E49" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -48440,10 +48890,10 @@
         <v>8</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -48467,10 +48917,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E51" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -48494,10 +48944,10 @@
         <v>4</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E52" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -48521,10 +48971,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E53" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -48548,10 +48998,10 @@
         <v>12</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E54" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -48575,10 +49025,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E55" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -48602,10 +49052,10 @@
         <v>8</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E56" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -48629,10 +49079,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E57" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -48656,10 +49106,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E58" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -48683,10 +49133,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E59" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -48710,10 +49160,10 @@
         <v>12</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E60" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -48730,36 +49180,36 @@
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B68" s="18" t="n">
         <v>1.31</v>
@@ -48768,12 +49218,12 @@
         <v>1.35</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B69" s="18" t="n">
         <v>1.59</v>
@@ -48782,12 +49232,12 @@
         <v>1.6</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B70" s="18" t="n">
         <v>0.8832</v>
@@ -48798,7 +49248,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B71" s="18" t="n">
         <v>1.34</v>
@@ -48809,7 +49259,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B72" s="18" t="n">
         <v>1.56</v>
@@ -48820,7 +49270,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B73" s="18" t="n">
         <v>1.45</v>
@@ -48831,7 +49281,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B74" s="18" t="n">
         <v>0.81</v>
@@ -48842,7 +49292,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B75" s="18" t="n">
         <v>1.87</v>
@@ -48853,7 +49303,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B76" s="18" t="n">
         <v>1.62</v>
@@ -48864,7 +49314,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B77" s="18" t="n">
         <v>3.86</v>
@@ -48872,7 +49322,7 @@
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B78" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.25)</f>
@@ -48885,7 +49335,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B79" s="14" t="n">
         <f aca="false">MEDIAN(B68:B77)</f>
@@ -48898,7 +49348,7 @@
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B80" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.75)</f>
@@ -48911,7 +49361,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B81" s="14" t="n">
         <f aca="false">MIN(B68:B77)</f>
@@ -48924,7 +49374,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B82" s="14" t="n">
         <f aca="false">MAX(B68:B77)</f>
@@ -48937,7 +49387,7 @@
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B83" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B78,C78),2)</f>
@@ -48946,7 +49396,7 @@
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B84" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B79,C79),2)</f>
@@ -48955,7 +49405,7 @@
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B85" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B80,C80),2)</f>
@@ -48964,7 +49414,7 @@
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B86" s="14" t="n">
         <f aca="false">ROUND(MIN(B81,C81),2)</f>
@@ -48973,7 +49423,7 @@
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B87" s="14" t="n">
         <f aca="false">ROUND(MAX(B82,C82),2)</f>
@@ -48982,48 +49432,48 @@
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C91" s="14" t="n">
         <f aca="false">B83</f>
         <v>1.33</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E91" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -49044,17 +49494,17 @@
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C92" s="14" t="n">
         <f aca="false">B84</f>
         <v>1.48</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E92" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -49075,17 +49525,17 @@
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C93" s="14" t="n">
         <f aca="false">B85</f>
         <v>1.61</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E93" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -49106,29 +49556,29 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B98" s="18" t="n">
         <v>9.57</v>
@@ -49138,12 +49588,12 @@
         <v>9.57</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B99" s="18" t="n">
         <v>4.61</v>
@@ -49153,12 +49603,12 @@
         <v>4.61</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B100" s="18" t="n">
         <v>2.54</v>
@@ -49168,12 +49618,12 @@
         <v>2.54</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B101" s="18" t="n">
         <v>30.2</v>
@@ -49183,12 +49633,12 @@
         <v>30.2</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B102" s="18" t="n">
         <v>16.2</v>
@@ -49200,7 +49650,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B103" s="18" t="n">
         <v>9.01</v>
@@ -49215,7 +49665,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B104" s="18" t="n">
         <v>22.6</v>
@@ -49230,7 +49680,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B105" s="18" t="n">
         <v>-10.6</v>
@@ -49242,7 +49692,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B106" s="18" t="n">
         <v>5.99</v>
@@ -49257,7 +49707,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B107" s="18" t="n">
         <v>10.5</v>
@@ -49272,7 +49722,7 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B108" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.25)</f>
@@ -49289,7 +49739,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B109" s="14" t="n">
         <f aca="false">MEDIAN(B98:B107)</f>
@@ -49306,7 +49756,7 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B110" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.75)</f>
@@ -49323,7 +49773,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B111" s="14" t="n">
         <f aca="false">MIN(B98:B107)</f>
@@ -49340,7 +49790,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B112" s="14" t="n">
         <f aca="false">MAX(B98:B107)</f>
@@ -49357,7 +49807,7 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B113" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(C108),2)</f>
@@ -49366,7 +49816,7 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B114" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(C109),2)</f>
@@ -49375,7 +49825,7 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B115" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(C110),2)</f>
@@ -49384,7 +49834,7 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B116" s="14" t="n">
         <f aca="false">ROUND(MIN(C111),2)</f>
@@ -49393,7 +49843,7 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B117" s="14" t="n">
         <f aca="false">ROUND(MAX(C112),2)</f>
@@ -49402,48 +49852,48 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="5" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C121" s="14" t="n">
         <f aca="false">B113</f>
         <v>5.99</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E121" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -49464,17 +49914,17 @@
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="5" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C122" s="14" t="n">
         <f aca="false">B114</f>
         <v>9.57</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="E122" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -49495,17 +49945,17 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C123" s="14" t="n">
         <f aca="false">B115</f>
         <v>16.2</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E123" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -49526,12 +49976,12 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49539,29 +49989,29 @@
         <v>28</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B130" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -49578,7 +50028,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B131" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -49595,7 +50045,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B132" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -49612,7 +50062,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B133" s="21" t="n">
         <f aca="false">Y!M29</f>
@@ -49629,7 +50079,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B134" s="21" t="n">
         <f aca="false">Y!N29</f>
@@ -49646,7 +50096,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B135" s="21" t="n">
         <f aca="false">Y!O29</f>
@@ -49663,27 +50113,27 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="5" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B137" s="19" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.201477501678979</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B138" s="21" t="n">
         <f aca="false">Y!D22/Y!D27*1000000</f>
@@ -49700,7 +50150,7 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B139" s="21" t="n">
         <f aca="false">Y!E22/Y!E27*1000000</f>
@@ -49717,7 +50167,7 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B140" s="21" t="n">
         <f aca="false">Y!F22/Y!F27*1000000</f>
@@ -49734,7 +50184,7 @@
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B141" s="21" t="n">
         <f aca="false">B133*(1-$B$137)</f>
@@ -49751,7 +50201,7 @@
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B142" s="21" t="n">
         <f aca="false">B134*(1-$B$137)</f>
@@ -49768,7 +50218,7 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B143" s="21" t="n">
         <f aca="false">B135*(1-$B$137)</f>
@@ -49785,7 +50235,7 @@
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B144" s="21" t="n">
         <f aca="false">SUMPRODUCT(B138:B143,1/(1+tp_r)^{1;2;3;4;5;6})+B143*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -49800,12 +50250,12 @@
         <v>1189912.86088635</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B145" s="21" t="n">
         <f aca="false">B144*(1+tp_r)</f>
@@ -49822,36 +50272,36 @@
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B146" s="25" t="n">
         <f aca="false">tp_wA*B145+tp_wB*C145+tp_wC*D145</f>
         <v>3709129.83314453</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>33</v>
@@ -49859,19 +50309,19 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C150" s="18" t="n">
         <v>1.26</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>59</v>
@@ -49879,19 +50329,19 @@
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="5" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C151" s="18" t="n">
         <v>3.35</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>59</v>
@@ -49899,19 +50349,19 @@
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="5" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C152" s="18" t="n">
         <v>2.22</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>59</v>
@@ -49919,19 +50369,19 @@
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="5" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C153" s="18" t="n">
         <v>1.66</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>59</v>
@@ -49939,55 +50389,55 @@
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="5" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B154" s="14" t="n">
         <f aca="false">MEDIAN(C150:C153)</f>
         <v>1.94</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B155" s="21" t="n">
         <f aca="false">tp_wA*Y!E28+tp_wB*Y!H28+tp_wC*Y!K28</f>
         <v>1271423.19481313</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B156" s="25" t="n">
         <f aca="false">B154*B155</f>
         <v>2466560.99793747</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="5" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B157" s="21" t="n">
         <f aca="false">tp_wA*(2/12*Y!D29+10/12*Y!E29)+tp_wB*(2/12*Y!G29+10/12*Y!H29)+tp_wC*(2/12*Y!J29+10/12*Y!K29)</f>
         <v>439185.328192061</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49995,29 +50445,29 @@
         <v>28</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C160" s="13"/>
       <c r="D160" s="13"/>
       <c r="E160" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="5" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B161" s="25" t="n">
         <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*B156</f>
         <v>3087845.415541</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B162" s="21" t="n">
         <f aca="false">B156</f>
@@ -50026,31 +50476,31 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="5" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B163" s="21" t="n">
         <f aca="false">cons_tp</f>
         <v>3096288</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="5" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B164" s="19" t="n">
         <f aca="false">B161/px-1</f>
         <v>1.41804652744009</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="5" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B165" s="19" t="n">
         <f aca="false">B162/px-1</f>
@@ -50059,7 +50509,7 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B166" s="26" t="n">
         <f aca="false">B145/px</f>
@@ -50074,36 +50524,36 @@
         <v>1.02498367030147</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="5" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B167" s="19" t="n">
         <f aca="false">B155/cons_bvps28-1</f>
         <v>-0.0906103007832535</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B168" s="19" t="n">
         <f aca="false">B157/(2/12*cons_eps27+10/12*cons_eps28)-1</f>
         <v>-0.167585820576288</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="5" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B169" s="19" t="n">
         <f aca="false">(cons_tp/cons_bvps28)/B154-1</f>
@@ -50116,19 +50566,19 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="5" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B170" s="27" t="str">
         <f aca="false">TEXT(D145,"#,##0")&amp;"～"&amp;TEXT(B145,"#,##0")</f>
         <v>1,308,904～6,513,978</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="5" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B171" s="15" t="n">
         <f aca="false">IF(px/Y!E28&gt;=MAX($B$68:$B$77),1,IF(px/Y!E28&lt;=MIN($B$68:$B$77),0,PERCENTRANK($B$68:$B$77,px/Y!E28)))</f>
@@ -50143,12 +50593,12 @@
         <v>0.185</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B172" s="0" t="str">
         <f aca="false">"DCF：股東現金流 2027–2029 用每股（淨利＋折舊－資本支出），2030–2032 收斂期用 EPS ×（1 − g／ROE），r 10%、g 4%、ROE 為 2023–2025 平均（含 2023 虧損年）；明確期＋永續，基準日 2026 年底。Comparable：三星、美光、鎧俠、南亞科前瞻 P/B 中位數 × 2028 年底每股淨值（情境加權）。收斂期（2030–2032）淨利率"&amp;"收斂到循環中段：A 十年平均 × 1.2、B 十年平均、C 十年平均 × 0.8（In 頁 cyc_mA／cyc_mC），永續期以 2032 中段水準為基礎。偏誤：2027–2029 仍為高峰期盈餘且權重大，DCF 仍可能偏高估；同業 P/B 為循環高峰前的市場倍數、且 SK 海力士淨值增速高於同業，Comparable 方向不明。情境對應：A＝順利、B＝平平、C＝不如預期（原為 TrendFor"&amp;"ce／BofA 型價格情境）。"&amp;IF(MAX(B166:D166)&gt;3,"注意：DCF ÷ 現價有情境高於 3 倍（見上方「DCF ÷ 現價」列）；DCF 對收斂期淨利率與永續假設敏感，宜與 Comparable、市場共識並讀。","")</f>
@@ -50157,7 +50607,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50165,29 +50615,29 @@
         <v>28</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C175" s="13"/>
       <c r="D175" s="13"/>
       <c r="E175" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="5" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B176" s="21" t="n">
         <f aca="false">tp_wA*B178+tp_wB*B179+tp_wC*B180</f>
         <v>1392208.55280262</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B177" s="19" t="n">
         <f aca="false">B176/px-1</f>
@@ -50196,7 +50646,7 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="5" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B178" s="21" t="n">
         <f aca="false">B85*Y!D28</f>
@@ -50209,7 +50659,7 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B179" s="21" t="n">
         <f aca="false">B84*Y!G28</f>
@@ -50222,7 +50672,7 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="5" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B180" s="21" t="n">
         <f aca="false">B83*Y!J28</f>
@@ -50235,7 +50685,7 @@
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B181" s="15" t="n">
         <f aca="false">tp_wA</f>
@@ -50256,34 +50706,34 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B184" s="27" t="str">
         <f aca="false">IF(B164&gt;0.5,"大於 50%",IF(B164&gt;0.25,"25%–50%",IF(B164&gt;=0,"0%–25%",IF(B164&gt;=-0.25,"0%～−25%",IF(B164&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>大於 50%</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B185" s="27" t="str">
         <f aca="false">IF(B164&gt;0.5,"強力買進",IF(B164&gt;0.25,"買進",IF(B164&gt;=-0.25,"中立",IF(B164&gt;=-0.5,"放空","強力放空"))))</f>
         <v>強力買進</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
   </sheetData>
@@ -50311,29 +50761,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>31</v>
@@ -50345,10 +50795,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -50365,10 +50815,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -50385,10 +50835,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -50405,10 +50855,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -50425,10 +50875,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -50445,10 +50895,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -50465,7 +50915,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>31</v>
@@ -50477,10 +50927,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -50497,10 +50947,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -50517,10 +50967,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -50537,10 +50987,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -50557,10 +51007,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -50577,10 +51027,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -50597,7 +51047,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>31</v>
@@ -50609,10 +51059,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -50629,10 +51079,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -50649,10 +51099,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -50669,10 +51119,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -50689,10 +51139,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -50709,10 +51159,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -50729,7 +51179,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>31</v>
@@ -50741,10 +51191,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -50761,10 +51211,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -50781,10 +51231,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -50801,10 +51251,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -50821,10 +51271,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -50841,10 +51291,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -50861,32 +51311,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50894,7 +51344,7 @@
         <v>31</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -50915,10 +51365,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C41" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r+0.01))^1+Val!B139/(1+(tp_r+0.01))^2+Val!B140/(1+(tp_r+0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C138/(1+(tp_r+0.01))^1+Val!C139/(1+(tp_r+0.01))^2+Val!C140/(1+(tp_r+0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D138/(1+(tp_r+0.01))^1+Val!D139/(1+(tp_r+0.01))^2+Val!D140/(1+(tp_r+0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -50939,10 +51389,10 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C42" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r-0.01))^1+Val!B139/(1+(tp_r-0.01))^2+Val!B140/(1+(tp_r-0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C138/(1+(tp_r-0.01))^1+Val!C139/(1+(tp_r-0.01))^2+Val!C140/(1+(tp_r-0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D138/(1+(tp_r-0.01))^1+Val!D139/(1+(tp_r-0.01))^2+Val!D140/(1+(tp_r-0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -50963,10 +51413,10 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C43" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -50987,10 +51437,10 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C44" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -51011,10 +51461,10 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C45" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -51035,10 +51485,10 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C46" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -51059,7 +51509,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C47" s="28" t="n">
         <f aca="false">C40-Val!B146</f>
@@ -51091,7 +51541,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51099,21 +51549,21 @@
         <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Y!C4</f>
@@ -51127,12 +51577,12 @@
         <v>-0.00836946403295669</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!C14</f>
@@ -51146,12 +51596,12 @@
         <v>-0.000839616405542865</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!C20</f>
@@ -51165,12 +51615,12 @@
         <v>0.0337735275745357</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!C6</f>
@@ -51184,12 +51634,12 @@
         <v>-0.107661421776805</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!D4</f>
@@ -51203,12 +51653,12 @@
         <v>0.000398596474166402</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D14</f>
@@ -51222,12 +51672,12 @@
         <v>0.0515932496365124</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -51241,12 +51691,12 @@
         <v>0.0130416064099912</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!E14</f>
@@ -51260,12 +51710,12 @@
         <v>0.0571960438943868</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Q!H4</f>
@@ -51279,12 +51729,12 @@
         <v>0.0234999470244424</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">Q!H10</f>
@@ -51298,12 +51748,12 @@
         <v>-0.000178817722798708</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -51318,12 +51768,12 @@
         <v>0.156215042736661</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B15" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -51338,12 +51788,12 @@
         <v>0.328899445317256</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B16" s="17" t="n">
         <f aca="false">Y!E28</f>
@@ -51358,7 +51808,7 @@
         <v>0.0790737443350025</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>
